--- a/QuickRegressionTesting5.xlsx
+++ b/QuickRegressionTesting5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aswathy.n/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thermofisher-my.sharepoint.com/personal/aswathy_n_thermofisher_com/Documents/Aswathy (1)/My_learning/programming_learning/GL_AIML/KeyAreas/GitHub_CICDLearning/RegressionScripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A84F89-77DE-E94A-B7B2-4ADE76FB0224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{27A84F89-77DE-E94A-B7B2-4ADE76FB0224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{287D984B-1D2B-8344-9837-7C3E531BB795}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="760" windowWidth="27720" windowHeight="16940" firstSheet="3" activeTab="4" xr2:uid="{F1B42ADB-BE16-DF45-8356-FD35A5FE073C}"/>
+    <workbookView xWindow="44860" yWindow="2860" windowWidth="27720" windowHeight="16940" firstSheet="3" activeTab="4" xr2:uid="{F1B42ADB-BE16-DF45-8356-FD35A5FE073C}"/>
   </bookViews>
   <sheets>
     <sheet name="URLSheet" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="QA_Trials" sheetId="10" r:id="rId11"/>
     <sheet name="Prod_trials" sheetId="7" r:id="rId12"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">QA_Trials!#REF!</definedName>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="349">
   <si>
     <t>URL</t>
   </si>
@@ -677,16 +678,6 @@
 1. Evaluation of a Novel Agar Medium from Remel to Screen for Methicillin Resistant Staphylococcus aureus (Page: 1, 2, 3)
 2. Comparison of Four Media for the Detection of Methicillin-Resistant Staphylococcus aureus (MRSA) from Nasal Swabs (Page: 1, 2, 3)
 3. Spectra MRSA (Page: 1, 2)</t>
-  </si>
-  <si>
-    <t>What are some of the common Python packages included in the AutoScript package?</t>
-  </si>
-  <si>
-    <t>AUTOSCRIPT4</t>
-  </si>
-  <si>
-    <t>Common Python Packages Included in AutoScript
-AutoScript is built upon Python 3.5 and includes a number of pre-installed libraries for scientific computing, data analysis, data visualization, image processing, and machine learning.</t>
   </si>
   <si>
     <t>Physical and Chemical Characteristics RINGERS SOLUTION BR0052G ?</t>
@@ -1205,203 +1196,34 @@
     <t>How to link personal and business account?</t>
   </si>
   <si>
-    <t>Linking Your Personal and Business Accounts
-To link your personal and business accounts, follow these steps:
-Step 1: Create a Personal Account
-Hover over 'Sign In' at the top of the page and select 'Create Personal Account.'
-Fill out the form using your business email address and then select 'Create Account.'
-You will receive an email verification for security.
-Step 2: Create a Business Account
-Sign in to your personal account at the top of the page and open the 'My Account' menu.
-Select 'Upgrade to a Business Account.' You will then either link to an existing business account or register a new business account.
-To link to an existing business account, enter a new address to link to an existing business account.
-To register a new business account, complete the following fields:
-Billing Info: Provide billing address, contact details, and Federal Tax Number. Indicate if tax-exempt and upload relevant documents.
-Shipping Info: Provide shipping address and contact information.
-Representative: Include your Fisher Scientific Representative's name if applicable.
-Company Info: Answer questions about your company.
-Submit: Review, accept terms, and click 'Submit.'
-Sources 1
-Additional Data &amp; References
-1. Creating an Account
-2. Applying Contract Pricing
-3. How to Upgrade to a Business Account</t>
-  </si>
-  <si>
     <t>how to change my shipping address?</t>
   </si>
   <si>
-    <t>Changing Your Shipping Address
-To change your shipping address, follow these steps:
-Log in to your fishersci.com account.
-Navigate to 'My Account' on the top right of the webpage or from your Account Dashboard.
-Select 'Add New Address' from the dropdown menu.
-Complete and submit the Shipping Address section of the form. As you type, any existing accounts that match your address will appear for you to select. If no matches are found, a new account will be created for that delivery address.
-You can track all accounts on your Business Accounts page.
-Sources 1
-Additional Data &amp; References
-1. Account Address Changes
-2. Help &amp; Support Center
-3. Managing Subscription Orders</t>
-  </si>
-  <si>
     <t>how to do fund tracking? if I am not an admin? How to use search?</t>
   </si>
   <si>
-    <t>Tracking Funds and Using the Search Function
-Tracking Funds
-As a fund administrator, you can use the Fund Tracking Dashboard to add new funds, view and edit existing funds, download spend reports, and browse detailed fund histories. Once funds are set up and users are assigned to them, users and approvers in your organization can view the details of these funds and allocate purchases to them.
-Using the Search Function
-To search for products, enter a keyword, catalog number, CAS number, or manufacturer part number in the search box located in the blue bar at the top of the site and either hit enter or click on the magnifying glass to the right of the box. You can narrow down your results by selecting one of the refinement filters from the left-hand side of your search results. Filters include category, special offers, special interest, and brands. Depending on the product category, other filters may appear such as capacity, material, and more.
-Sources 2 3
-Additional Data &amp; References
-1. Help &amp; Support Center
-2. Tracking Funds
-3. Understanding User Types
-4. Using the User Management Dashboard</t>
-  </si>
-  <si>
     <t>can I place orders without having an account?</t>
   </si>
   <si>
-    <t>Placing Orders Without an Account
-You can place orders directly through fishersci.com with or without an account. However, customers with a fishersci.com profile with a linked business account have access to a variety of powerful features that make ordering products fast and easy, including:
-Account-specific prices
-Real-time product availability
-Estimated delivery dates
-Online quotes
-Save and share product lists
-Secure payment options
-Learn how to create an account
-You can also place orders through your eProcurement system.
-Sources  3
-Additional Data &amp; References
-1. Help &amp; Support Center
-2. Account &amp; Settings
-3. Orders &amp; Returns
-4. Viewing Orders Without Signing In
-5. Ordering Through an eProcurement System
-6. Creating an Account</t>
-  </si>
-  <si>
     <t>How do I become an administrator?</t>
   </si>
   <si>
-    <t xml:space="preserve">To become an administrator for your organization’s business account, contact Website Support through the contact links on the Help and Support homepage below.
-FAQ: Creating User Groups
-</t>
-  </si>
-  <si>
     <t>what is the price of NP0001</t>
   </si>
   <si>
-    <t>This search is not yet optimized to provide product information, please feel free to ask specific questions about 'how to' topics such as accounts, documentation, quotes, and orders to name a few.</t>
-  </si>
-  <si>
     <t>do you have customer care contact details?</t>
   </si>
   <si>
-    <t>Click here to access contact information to reach our team.</t>
-  </si>
-  <si>
     <t>do you have manuals for 11960077</t>
   </si>
   <si>
-    <t>I found the following Manuals for 11960077
-Product Information (1 matches)
-Instructions for Use: DMEM (Dulbecco's Modified Eagle Medium)</t>
-  </si>
-  <si>
     <t>How to login if i forgot my password? How to track my orders?</t>
   </si>
   <si>
-    <t>User is asking for assistance with logging in after forgetting their password.
-Resetting Your Password
-If you have forgotten your password, follow these steps to reset it:
-Sign in to your account and select Password and Security from the My Account dropdown.
-Scroll down to Change Password (hyperlink just below the current password field).
-You will be asked to confirm that you would like to change your password. You will then receive a 'Forgot Password' email.
-Once you receive the email, follow the prompt to update your password.
-Requirements for password strength:
-Must have at least one lower-case letter
-Must have at least one capital letter
-Must have at least one number
-Must have at least one special character
-Must not include spaces
-Must be at least 9 characters long
-Sources  2
-Additional Data &amp; References
-1. Help &amp; Support Center
-2. Changing Your Password
-3. Signing In and Account Protection
-4. How to Upgrade to a Business Account
-5. Tracking Funds
-6. Changing Your Security Question
-LikeDislike
-Give feedback
-User is asking for assistance with tracking their orders.
-Tracking an Order
-To track your order, follow these steps:
-Navigate to the Order Status tool at the top of the website.
-Log in or enter your order number and ZIP code.
-Once you select an order, you will be brought to a page with your order details, including tracking information.
-For more detailed information, you can also visit the Tracking an Order page.
-Sources  1  7
-Additional Data &amp; References
-1. Viewing Orders Without Signing In
-2. Managing Subscription Orders
-3. Ordering Through fishersci.com
-4. Using My Lists
-5. Returning an Order
-6. Orders &amp; Returns
-7. Viewing Your Order History
-8. Ordering Through an eProcurement System</t>
-  </si>
-  <si>
     <t>do you have brochures and sds for NP0001</t>
   </si>
   <si>
-    <t>User is requesting brochures and safety data sheets for NP0001.
-I found the following Brochures for NP0001
-Scientific Resources (1 matches)
-Brochure: Nunc Cell Factory Systems
-LikeDislike
-Give feedback
-User is requesting brochures and safety data sheets for NP0001.
-I found the following safety_data_sheets for NP0001
-Safety Data Sheets (2 matches)
-SampleSDS
-NP0001</t>
-  </si>
-  <si>
     <t>SR0083A Certs</t>
-  </si>
-  <si>
-    <t>Certificates (5 matches)
-Lot #
-Certificate Type
-Date
-Catalog Number(s)
-3578121
-Certificate of Analysis
-Feb 20, 2023
-SR0083A
-3570166
-Certificate of Analysis
-Dec 08, 2022
-SR0083A
-3517625
-Certificate of Analysis
-Aug 30, 2022
-SR0083A
-3361555
-Certificate of Analysis
-Nov 19, 2021
-SR0083A
-2175950
-Certificate of Analysis
-May 21, 2021
-SR0083A</t>
   </si>
   <si>
     <t>Prod discontinued</t>
@@ -2691,12 +2513,637 @@
 75003180	TX-750 4 x 750 mL Swinging Bucket Rotor	$4,020.00	In Stock
 75005756	1.5/2 mL Microtube Adapter for MicroClick 18 x 5 Rotor (Pack of 2)	$166.00	Out Of Stock (Pending)</t>
   </si>
+  <si>
+    <t>Here is the contact information to reach our team.
+How can we help?
+Customer Service
+800 955 6288
+Customercare@thermofisher.com
+Technical Support
+800 955 6288
+Contact Technical Support
+Instrument Service
+800 955 6288
+Contact Instrument Service
+Give feedback</t>
+  </si>
+  <si>
+    <t>Product NP0006 (NuPAGE‚Ñ¢ Transfer Buffer (20X)) is currently In Stock and available for purchase. i
+Give feedback</t>
+  </si>
+  <si>
+    <t>Currently, there are no active promotions or discounts available for product NP0006 (NuPAGE‚Ñ¢ Transfer Buffer (20X)).
+Give feedback</t>
+  </si>
+  <si>
+    <t>I found the following safety_data_sheets for NP0006
+Safety Data Sheets (1 matches)
+NP0006
+Give feedback</t>
+  </si>
+  <si>
+    <t>Certificates (5 matches)
+Lot #
+Certificate Type
+Date
+Catalog Number(s)
+TFHEPUY
+Certificate of Analysis
+Apr 02, 2026
+NP0006
+TF2C1GM
+Certificate of Analysis
+Apr 02, 2026
+NP0006
+TFQAIIRKW
+Certificate of Analysis
+Mar 29, 2026
+NP0006
+TFOT1DT
+Certificate of Analysis
+Mar 27, 2026
+NP0006
+TF8AAQW
+Certificate of Analysis
+Mar 27, 2026
+NP0006
+Here are the 5 latest certificate(s). If you can't find the one you're looking for, please provide the LOT number below.
+Give feedback</t>
+  </si>
+  <si>
+    <t>I found the following Manuals for NP0006
+Product Information (5 matches)
+Quick Reference Guide: NuPAGE Bis-Tris Midi Gels, WedgeWell Format
+Quick Reference Guide: NuPAGE Bis-Tris Midi Gels
+NuPAGE Technical Guide
+NuPAGE Large Protein Analysis System
+Mini Gel Tank and Blot Module QRC
+Give feedback</t>
+  </si>
+  <si>
+    <t>Attribute NP0006 3500
+Catalog Number NP0006 3500
+Product Title NuPAGE‚Ñ¢ Transfer Buffer (20X) HLT 10 MICROPOINT BULK NST 100
+Product Size Each Case of 10000
+Unit of Measure EA CS
+Price (USD) $36.81 Price is not available
+Availability In Stock Not specified
+Is Loyalty Aspire Eligible True False
+Is Recurring Order Eligible True False
+Product Type / Category Transfer Buffer Not specified
+Specifications Buffer: Transfer Buffers
+Concentration: 20X
+Content And Storage: Store at room temperature. Guaranteed stable for 6 months unless otherwise specified.
+Gel Compatibility: NuPAGE‚Ñ¢ Gels
+Quantity: 125mL
+Shelf Life: 6 Months
+Shipping Condition: Room Temperature
+Gel Type: NuPAGE
+Product Line: NuPAGE Not specified
+Give feedback</t>
+  </si>
+  <si>
+    <t>Technical Notes
+There are no specific technical notes provided for product NP0006 in the available documentation.
+Sources 1
+Additional Data &amp; References
+1. NuPAGE Large Protein Analysis System (Page: 9, 16, 32, 34)
+2. 2D Gel Electrophoresis Buffers &amp; Reagents
+3. 2D Gel Electrophoresis Buffers &amp; Reagents
+4. NuPAGE Technical Guide (Page: 56)
+5. Western Blot Protocols and Recipes
+Give feedback</t>
+  </si>
+  <si>
+    <t>Brochures Available for Western Blotting and Protein Electrophoresis
+We offer several brochures that provide detailed information and guidance on western blotting and protein electrophoresis workflows, including transfer buffers and detection reagents.
+Western Blotting Overview Brochure: This brochure provides an overview of the western blotting workflow, helping users understand the process and optimize their experiments.
+HMW Protein Transfer Application Note: This application note focuses on the transfer of high molecular weight proteins using the iBlot 2 system.
+Western Detection Workflow Brochure: This brochure covers the entire western detection workflow, including blocking buffers, wash buffers, and stripping buffers.
+These brochures can be downloaded from our website and provide valuable insights for optimizing western blot experiments.
+Sources 2
+4
+Additional Data &amp; References
+1. NuPAGE Large Protein Analysis System (Page: 32)
+2. Transfer Buffers for Western Blotting
+3. Native PAGE Gels
+4. Western Blot Buffers
+5. NuPAGE Technical Guide (Page: 3, 56)
+6. Blocking Buffers for Western Blot and ELISA
+7. NuPAGE Technical Guide (Page: 56)
+Give feedback</t>
+  </si>
+  <si>
+    <t>Contents of the Collibri ES DNA Library Preparation Kit Documentation
+The documentation includes detailed protocols and information sections such as:
+Purify the amplified SARS-CoV-2 genome
+Normalize amplified SARS-CoV-2 genome
+Prepare 96 indexed libraries
+Fragmentation and dA-tailing of input DNA
+Dual indexed adaptor ligation
+Post-ligation cleanup
+Library PCR amplification (optional)
+Purify amplified DNA libraries
+Verify quality and quantity of prepared DNA libraries
+Sequence on an Illumina platform
+Adaptor index sequences and plate layouts
+Chemical and biological hazard safety
+Customer and technical support
+Limited product warranty
+This documentation serves as a comprehensive guide for library preparation and sequencing workflows.
+Sources 1
+2
+Additional Data &amp; References
+1. User Guide: Collibri ES DNA Library Prep Kit - for sequencing SARS-CoV-2 with PCR enrichment (Page: 4, 27, 52)
+2. User Guide: Collibri ES DNA Library Prep Kit - For sequencing SARS-CoV-2 with PCR enrichment using Phusion Plus PCR Master Mix (Page: 4, 49)
+3. User Guide: Collibri ES DNA Library Prep Kits for Whole Exome Sequencing (Page: 29)
+4. User Guide: Collibri ES DNA Library Prep Kit for Illumina (Page: 5, 58)
+Give feedback</t>
+  </si>
+  <si>
+    <t>I was unable to find specific information about the vitamins and their molecular weights in the provided product documentation for catalog number 11012044. Please contact our Technical Support Team for detailed information.
+Sources i
+Additional Data &amp; References
+1. Product Sheet: Media and Balanced Salt Solutions Preparation from Powder and Concentrates (Page: 1, 2, 3)
+2. FAQ:Where can I find media formulations?
+3. FAQ:Where can I find the osmolality for MEM Medium?
+4. FAQ:Do you have a comparison of dishes, culture plates, and flasks by surface area, seeding density, cells at confluency, and volumes of Versene solution, trypsin, and growth medium?
+5. FAQ:Can the Gibco Media Configurator be used for my own proprietary formulation?
+6. FAQ:Do you offer assistance with media formulation development?
+How can we help?
+Customer Service
+800 955 6288
+Customercare@thermofisher.com
+Technical Support
+800 955 6288
+Contact Technical Support
+Sales
+Live Chat
+Give feedback</t>
+  </si>
+  <si>
+    <t>Concentration of NuPAGE Transfer Buffer (20X) - NP0006
+The concentration of the NuPAGE Transfer Buffer (catalog number NP0006) is 20X.
+This buffer is designed for transferring proteins from NuPAGE Bis-Tris and NuPAGE Tris-Acetate gels to membranes for western blotting, maintaining a neutral pH environment during electrophoresis.
+Additional Data &amp; References
+1. Western Blot Protocols and Recipes
+2. NuPAGE Technical Guide (Page: 8, 48)
+3. NuPAGE Technical Guide (Page: 8, 48)
+4. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels (Page: 1)
+5. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels, WedgeWell Format (Page: 1)
+6. Western Blot Sample Preparation Protocol
+Give feedback</t>
+  </si>
+  <si>
+    <t>Related Products to NP0006 (NuPAGE Transfer Buffer 20X)
+The following electrophoresis reagents and apparatus are related and commonly used with NP0006 for protein separation and analysis:
+Product Quantity Catalog Number
+XCell SureLock_x0002_1 Mini-Cell 1 unit EI0001
+XCell II_x0002_1 Blot Module 1 unit EI9051
+PowerEase_x0002_1 500 Power Supply 1 unit EI8600
+DryEase_x0002_1 Mini-Gel Drying System 1 Kit NI2387
+StainEase_x0002_1 Staining Tray 2/pack NI2400
+Gel-Dry_x0002_1 Drying Solution 500 mL LC4025
+iBlot_x0002_1 Gel Transfer Device 1 unit IB1001
+Novex_x0002_1 Semi-Dry Blotter 1 unit SD1000
+NuPAGE_x0002_1 LDS Sample Buffer (4X) 10 mL NP0007
+250 mL NP0008
+NuPAGE_x0002_1 MOPS SDS Running Buffer (20X) 500 mL NP0001
+NuPAGE_x0002_1 MES SDS Running Buffer (20X) 500 mL NP0002
+NuPAGE_x0002_1 Tris-Acetate SDS Running Buffer (20X) 500 mL LA0041
+NuPAGE_x0002_1 Antioxidant 15 mL NP0005
+NuPAGE_x0002_1 Sample Reducing Agent (10X) 250 _x0003_bcL NP0004
+10 mL NP0009
+Novex_x0002_1 Tris-Glycine Native Running Buffer (10X) 500 mL LC2672
+Novex_x0002_1 Tris-Glycine Native Sample Buffer (2X) 20 mL LC2673
+Nitrocellulose Membrane 0.2 _x0003_bcm 20 membrane/filter papers LC2000
+Invitrolon_x0002_1 PVDF membranes 0.45 _x0003_bcm 20 membrane/filter papers LC2005
+PVDF membranes 0.2 _x0003_bcm 20 membrane/filter papers LC2002
+Sources 1
+2
+Additional Data &amp; References
+1. NuPAGE Technical Guide (Page: 1, 48)
+2. NuPAGE Technical Guide (Page: 48)
+3. Western Blot Protocols and Recipes
+4. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels (Page: 1)
+5. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels, WedgeWell Format (Page: 1)
+6. NuPAGE Large Protein Analysis System (Page: 31)
+7. Western Blot Sample Preparation Protocol
+Give feedback</t>
+  </si>
+  <si>
+    <t>Comparison of NP0006 with NP0002 and NP0004
+Attribute NP0006 NP0002 NP0004
+Catalog Number NP0006 NP0002 NP0004
+Product Title NuPAGE‚Ñ¢ Transfer Buffer (20X) NuPAGE‚Ñ¢ MES SDS Running Buffer (20X) NuPAGE‚Ñ¢ Sample Reducing Agent (10X)
+Product Line NuPAGE NuPAGE NuPAGE
+Product Type Transfer Buffer Running Buffer Sample Reducing Agent
+Concentration 20X 20X 500 mM
+Quantity 125mL 500 mL 250ŒºL
+Storage Store at room temperature. Guaranteed stable for 6 months. +4¬∞C to 25¬∞C Store at 4¬∞C. Guaranteed stable for 6 months.
+Physical Form Not specified Liquid Not specified
+pH Not specified 7.3 Not specified
+Shipping Condition Room Temperature Not specified Wet Ice
+Price (USD) $36.81 $111.65 $20.65
+Availability In Stock In Stock In Stock
+Summary: While all three products belong to the NuPAGE product line, NP0006 is a Transfer Buffer, NP0002 is a MES SDS Running Buffer, and NP0004 is a Sample Reducing Agent. They serve different roles in electrophoresis workflows. NP0006 and NP0002 share the same concentration of 20X but differ in buffer type and volume. NP0004 has a different concentration and function. All are available in stock.
+Give feedback</t>
+  </si>
+  <si>
+    <t>Alternate Products for NP0006 (NuPAGE‚Ñ¢ Transfer Buffer (20X))
+Catalog Number Product Title Quantity Price (USD) Availability
+BT00061 Bolt‚Ñ¢ Transfer Buffer (20X) Each $240.65 In Stock
+This search is not yet fully optimized to provide product recommendations. Please feel free to ask specific questions about this product for more detailed information.
+i
+Give feedback</t>
+  </si>
+  <si>
+    <t>We have agents available now that can assist you with this query! Please connect with them by selecting the team available in the open chat window to get started.
+Give feedback</t>
+  </si>
+  <si>
+    <t>Detection of Binding Between MGP and BMP-2
+Binding between Matrix GLA protein (MGP) and bone morphogenetic protein-2 (BMP-2) can be detected using immunoprecipitation techniques. In the described study, MGP and BMP-2 were tagged with FLAG and c-Myc, respectively. Immunoprecipitation was performed using these tagged proteins, and the results showed co-precipitation of BMP-2 with MGP, indicating binding.
+Sources 1
+Additional Data &amp; References
+1. Matrix GLA protein, a regulatory protein for bone morphogenetic protein-2.
+2. NuPAGE Bis-Tris and Bolt Bis-Tris Plus Gels
+3. NuPAGE Tris-Acetate Gels
+4. Native PAGE Gels
+5. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels, WedgeWell Format (Page: 3)
+6. NuPAGE Technical Guide (Page: 36, 46)
+7. NuPAGE Technical Guide (Page: 36)
+Give feedback</t>
+  </si>
+  <si>
+    <t>Sterility of rhLaminin-521
+The provided product information does not include any details regarding the sterility of rhLaminin-521. Therefore, we cannot confirm if rhLaminin-521 is sterile based on the available data.
+For specific information about the sterility or other quality attributes of rhLaminin-521, we recommend consulting the product's Certificate of Analysis (COA) or contacting our Technical Support Team.
+Sources 1
+2
+3
+4
+5
+6
+Additional Data &amp; References
+1. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels (Page: 1)
+2. NuPAGE Large Protein Analysis System (Page: 4, 30, 31)
+3. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels, WedgeWell Format (Page: 1)
+4. Western Blot Protocols and Recipes
+5. Protein Electrophoresis Buffers and Reagents
+6. Protein Electrophoresis Buffers and Reagents
+How can we help?
+Customer Service
+800 955 6288
+Customercare@thermofisher.com
+Technical Support
+800 955 6288
+Contact Technical Support
+Instrument Service
+800 955 6288
+Contact Instrument Service
+Sales
+Live Chat
+Give feedback</t>
+  </si>
+  <si>
+    <t>Shipping Conditions for NuPAGE Sample Reducing Agent (Cat. No. NP0004)
+The product should be shipped on wet ice to maintain stability during transport.
+Additional Data &amp; References
+1. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels, WedgeWell Format (Page: 1, 4)
+2. Quick Reference Guide: NuPAGE Bis-Tris Mini Gels (Page: 1, 4)
+3. Quick Reference Guide: NuPAGE Bis-Tris Midi Gels (Page: 1, 4)
+4. Immunoprecipitation using Protein A - 10006D
+5. Immunoprecipitation using Protein G - 10007D
+Give feedback</t>
+  </si>
+  <si>
+    <t>Main Challenges Associated with cfDNA Library Preparation
+Circulating cell-free DNA (cfDNA) library preparation presents several challenges due to the nature of the input material and sample variability:
+Limited Quantity: cfDNA is present in very limited quantities in blood samples, typically in the low ng/mL range, making it difficult to obtain sufficient material for sequencing.
+Degraded DNA: cfDNA is often degraded because it is fragmented during apoptosis, resulting in short fragments (~170 bp), and further degradation can occur in peripheral circulation.
+Genomic DNA Contamination: Presence of genomic DNA (gDNA) from white blood cells due to mechanical damage during sample processing and storage can contaminate cfDNA samples, complicating the enrichment of cfDNA.
+Variability in cfDNA Amounts: There is considerable variation in cfDNA amounts depending on sample type, complicating workflow standardization.
+Low Quality of Input Material: The fragmented and degraded nature of cfDNA makes efficient and reproducible extraction essential for successful library preparation and downstream analysis.
+These challenges require specialized protocols and careful handling to ensure high-quality sequencing libraries from cfDNA.
+Sources 1
+Additional Data &amp; References
+1. Application note: Library preparation from circulating cell-free DNA (Page: 1, 2, 4)
+2. Tech Note: Scaling library preparation and maintaining quality (Page: 1, 2)
+3. Tech Note: Impact of GC bias on library preparation (Page: 1)
+4. User Guide: Collibri ES DNA Library Prep Kit for Illumina (Page: 15)
+5. FAQ:How do I assess the quality of the prepared Collibri DNA library?
+Give feedback</t>
+  </si>
+  <si>
+    <t>Fixation After Staining with LysoTracker Green DND-26
+LysoTracker Green DND-26 is a cell-permeable, non-fixable dye that stains acidic compartments such as lysosomes. Because it is non-fixable, the staining is not retained after fixation of cells. This means that if you fix the cells after staining with LysoTracker Green DND-26, the fluorescent signal will likely be lost.
+In contrast, some other LysoTracker probes, such as LysoTracker Red DND-99, usually retain their staining pattern following fixation with aldehydes.
+Summary
+LysoTracker Green DND-26: non-fixable, staining not retained after fixation.
+LysoTracker Red DND-99: staining usually retained after fixation.
+Therefore, if fixation after staining is required, consider using a fixable LysoTracker probe like LysoTracker Red DND-99 instead of LysoTracker Green DND-26.
+Sources 1
+Additional Data &amp; References
+1. Probes for Lysosomes, Peroxisomes and Yeast Vacuoles‚ÄîSection 12.3
+2. LysoTracker and LysoSensor Probes (Page: 1, 3, 4)
+3. Live intracellular super-resolution imaging using site-specific stains.
+4. Effect of cryopreservation of bovine sperm organelle function and viability as determined by flow cytometry.
+5. Comparative pathogenesis of haloacetic acid and protein kinase inhibitor embryotoxicity in mouse whole embryo culture.
+6. Fluorometric assessments of acrosomal integrity and viability in cryopreserved bovine spermatozoa.
+Give feedback</t>
+  </si>
+  <si>
+    <t>属性	NP0006	NP00061
+产品名称	NuPAGE™ Transfer Buffer (20X)	NuPAGE™ Transfer Buffer (20X), 1L
+规格浓度	20X	20X
+容量	125mL	1L
+价格 (USD)	36.81	243.00
+库存状态	In Stock	In Stock
+总结：两款产品均为20X浓度的NuPAGE转移缓冲液，主要区别在于容量和价格，NP0006为125mL，价格为36.81美元；NP00061容量为1L，价格为243.00美元。  i</t>
+  </si>
+  <si>
+    <t>Any publications that used IHC and WB for stem cell studies?</t>
+  </si>
+  <si>
+    <t>what are the latest publications on this product across the different journals?</t>
+  </si>
+  <si>
+    <t>Which all species this product  can be used?</t>
+  </si>
+  <si>
+    <t>Tell me about the  Species Reactivity across the different applications</t>
+  </si>
+  <si>
+    <t>are there any publications related to Immunohistochemistry application that talks about analyzing  ferritin levels?</t>
+  </si>
+  <si>
+    <t>any other primary antibody that can be used for similar applications, verified for efficiency and also cheaper?</t>
+  </si>
+  <si>
+    <t>which one is better MA1-110 or MA1-110-A647 in terms of western blotting usage?</t>
+  </si>
+  <si>
+    <t>any publications on western bloting application for the product MA1-110-A647</t>
+  </si>
+  <si>
+    <t>what are the recent published figures across the different applications and across different journals?</t>
+  </si>
+  <si>
+    <t>This is perfect! what is the Flow Cytometry (Flow) dilution?</t>
+  </si>
+  <si>
+    <t>what color is nuclear dna stain?</t>
+  </si>
+  <si>
+    <t>PA5-35380</t>
+  </si>
+  <si>
+    <t>which version of chatGPT is used here?</t>
+  </si>
+  <si>
+    <t>Is the conversion of astrocytes activated by nerve injuries to oligodendrocytes benficial?</t>
+  </si>
+  <si>
+    <t>The conversion of astrocytes activated by nerve injuries to oligodendrocytes is an area of ongoing research in neuroscience and regenerative medicine. Oligodendrocytes are cells responsible for forming myelin sheaths around axons in the central nervous system, which is important for nerve signal conduction. After nerve injury, damage to oligodendrocytes and myelin can affect nerve function.
+Astrocytes, another type of glial cell, become reactive in response to nerve injury. Research is investigating whether converting reactive astrocytes into oligodendrocytes may aid remyelination and nerve repair.
+Factors under study include:
+Functional integration of converted cells into neural tissue.
+Timing and extent of conversion without affecting other astrocyte functions.
+Type and severity of nerve injury.
+Potential side effects such as inflammation or glial cell imbalance.
+This topic remains under scientific investigation to clarify its benefits, mechanisms, and risks.
+Note: This information is for research context only and does not constitute medical advice.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I cannot share internal system or configuration details.</t>
+  </si>
+  <si>
+    <t>Color of Nuclear DNA Stain
+In the immunohistochemistry analysis using the Procollagen I C-Peptide Antibody (PA5-35380), the nuclear DNA is stained blue. This is shown in the image of fibrotic mouse lung tissue where the antibody staining is red, and the nuclear DNA stain is blue.
+Procollagen I C-Peptide Antibody (PA5-35380) in IHC
+Procollagen I C-Peptide Antibody (PA5-35380) in IHC: Immunohistochemistry analysis of COL1A1 Telopeptide in formaldehyde-fixed fibrotic mouse lung tissue. The antibody recognizes mature COL1A1 Telopeptide polyclonal antibody (Product # PA5-35380) with a dilution of 1:100 (red) that has formed fibrils in the extracellular matrix. The blue is staining nuclear DNA.
+Sources:
+Cross-talk between macrophages and smooth muscle cells impairs collagen and metalloprotease synthesis and promotes angiogenesis. (2016)</t>
+  </si>
+  <si>
+    <t>The recommended dilution for the Nestin antibody (Product # MA1-110) in Flow Cytometry (Flow) is 1:250 when used on human cells, as reported in a study using human neural stem cells derived from Parkinson's disease iPSCs.
+In the flow cytometry figures, the antibody was typically used at 1 µg/test (which corresponds to about 1:250 dilution depending on the volume) for 40 minutes at room temperature, followed by staining with a secondary antibody at 1:500 dilution.
+Here is an example from the literature:
+Species: Human
+Application: Flow Cytometry
+Dilution: 1:250
+Reference publication: PubMed ID 37996418
+Nestin Antibody (MA1-110) in Flow
+If you need dilution information for other species or specific protocols, please let me know.</t>
+  </si>
+  <si>
+    <t>Recent Published Figures for MA1-110 Across Different Applications and Journals
+Publication Title Year Journal Application
+Novel Variant Linked to Amyotrophic Lateral Sclerosis Risk and Clinical Phenotype 2021 Frontiers in Aging Neuroscience Immunocytochemistry
+Primary cilia and SHH signaling impairments in human and mouse models of Parkinson's disease 2022 Nature Communications Immunocytochemistry
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy 2023 Molecular Therapy Oncolytics Western Blot, Immunocytochemistry
+Representative Figures
+Nestin Antibody (MA1-110) in Immunocytochemistry (Frontiers in Aging Neuroscience 2021)
+Nestin Antibody (MA1-110) in ICC/IF
+Figure legend: Immunostaining of olfactory neurosphere derived cell lines showing Nestin expression and its variation in ALS patient-derived cells.
+Nestin Antibody (MA1-110) in Immunocytochemistry (Nature Communications 2022)
+Nestin Antibody (MA1-110) in ICC/IF
+Figure legend: Characterization of hiPSC derived neural precursor cells and neurons with Nestin staining.
+Nestin Antibody (MA1-110) in Western Blot (Molecular Therapy Oncolytics 2023)
+Nestin Antibody (MA1-110) in WB
+Figure legend: Western blot analysis showing reduction of stemness markers including Nestin in glioma stem-like cells after treatment.
+Nestin Antibody (MA1-110) in Immunocytochemistry (General Application)
+Nestin Antibody (MA1-110) in ICC/IF
+Figure legend: Immunofluorescent analysis of Nestin in U251 cells showing cytoskeletal localization.
+Nestin Antibody (MA1-110) in Western Blot (General Application)
+Nestin Antibody (MA1-110) in Western Blot
+Figure legend: Western blot showing relative expression of Nestin in iPSC, NSC, and NSC differentiated to neurons.
+Summary: The MA1-110 antibody has been used in recent years across multiple journals and applications including immunocytochemistry and western blot. The figures demonstrate its utility in neural stem cell and disease model studies, with clear visualization of Nestin expression patterns. Sources:
+Novel Variant Linked to Amyotrophic Lateral Sclerosis Risk and Clinical Phenotype (2021)
+Primary cilia and SHH signaling impairments in human and mouse models of Parkinson's disease (2022)
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy (2023)</t>
+  </si>
+  <si>
+    <t>Publications Reporting Western Blot Application for MA1-110-A647
+There is at least one recent publication citing the use of MA1-110-A647 in western blot applications:
+Publication Title Year Journal
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy 2023 Molecular Therapy Oncolytics
+This study investigated glioma stem-like cells and used MA1-110-A647 for western blot among other applications.
+Source:
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy (2023)</t>
+  </si>
+  <si>
+    <t>Comparison of MA1-110 and MA1-110-A647 for Western Blot Usage
+Based on available publication data, the antibody MA1-110 (Nestin monoclonal antibody) has been widely used and validated for western blot applications. It has been used successfully to detect Nestin protein bands in various cell lysates, including human neural stem cells and differentiated neurons, with clear bands observed around 160-250 kDa depending on the sample and gel system.
+In contrast, there is limited direct publication data comparing MA1-110-A647 specifically for western blot. The "-A647" suffix typically indicates a fluorophore conjugation (Alexa Fluor 647), which is more commonly used for fluorescence-based applications such as immunocytochemistry or flow cytometry rather than western blotting. Fluorophore-conjugated antibodies are generally less common for western blot unless specialized fluorescence detection systems are used.
+Therefore, for western blotting, MA1-110 (unconjugated) is the better validated and more commonly used option according to the literature. If fluorescence-based western blot detection is desired, MA1-110-A647 could be considered but may require compatible imaging equipment and optimization.
+Supporting Figure Example for MA1-110 in Western Blot
+Nestin Antibody (MA1-110) Western Blot
+Figure legend: Western blot analysis of Nestin using MA1-110 showing a band at ~250 kDa in SH-SY5Y cell lysate.
+Sources:
+An epilepsy-associated ACTL6B variant captures neuronal hyperexcitability in a human induced pluripotent stem cell model (2021)
+SIRT1 regulates sphingolipid metabolism and neural differentiation of mouse embryonic stem cells (2021)</t>
+  </si>
+  <si>
+    <t>Alternative Primary Antibodies for Similar Applications to MA1-110 (Nestin) in Stem Cell Studies
+Based on publication data, several other primary antibodies have been used for immunohistochemistry (IHC), immunocytochemistry (ICC), and western blot (WB) in stem cell and neural differentiation studies that may serve as alternatives to MA1-110:
+Antibody Catalog Number Target / Description Applications Species
+MA1-014 Nestin (alternative clone) IHC, ICC Human, Not Applicable
+14-9811-37, 14-9811-80, 14-9811-82, 14-9811-95 Stem cell markers including SOX2, CD133, OCT4 IHC, ICC Human
+pa5-114941, pa5-27438, pa5-41830, pa5-78440 Various stem cell and neural markers WB, ICC Human
+ma5-32447 Nestin ICC Human
+These antibodies have been cited in publications for stem cell and neural differentiation research and may offer comparable performance. Pricing and efficiency details should be checked on the product pages for cost comparison.
+Example Publication Using MA1-014 as Alternative
+Kimura et al. (2021) used MA1-014 for immunocytochemistry in human iPSC-derived neuronal cells to study neuronal differentiation and glycoprotein changes.
+Nestin Antibody MA1-110 in ICC/IF
+Figure legend: Immunofluorescence assays showing Nestin and other neural markers in iPSC-derived neural stem cells and progenitors.
+For detailed pricing and datasheets, please refer to the respective product pages on the Thermo Fisher website.
+Sources:
+Glycoproteomic analysis of neuronal differentiation in human iPSCs (2021)
+Stem cell phenotype predicts therapeutic response in glioblastomas (2022)
+Epilepsy-associated ACTL6B variant in iPSC model (2021)</t>
+  </si>
+  <si>
+    <t>Related Products Applied in Western Blot (WB) with MA1-110
+The product MA1-110 (Nestin monoclonal antibody) has been cited in multiple publications for use in Western Blot applications. Here are some key findings and related products used in WB:
+Publication Application Details
+CPNE7-Induced Autophagy Restores the Physiological Function of Mature Odontoblasts (2021) Western blot using MA1-110 for detection of Nestin in human dental pulp cells.
+SIRT1 regulates sphingolipid metabolism and neural differentiation of mouse embryonic stem cells (2021) Western blot with MA1-110 in mouse embryonic stem cells at 1:1000 dilution.
+EGF signaling promotes the lineage conversion of astrocytes into oligodendrocytes (2022) Western blot and immunocytochemistry using MA1-110.
+Regulatory Mechanism between Ferritin and Mitochondrial Reactive Oxygen Species (2023) Western blot with MA1-110 in human spinal ligament-derived cells.
+Human cytomegalovirus infection perturbs neural progenitor cell fate (2023) Western blot and immunocytochemistry with MA1-110 in human neural progenitor cells.
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy (2023) Western blot using MA1-110 and related variants.
+Representative Western Blot Images Using MA1-110
+Nestin Antibody (MA1-110) in WB
+Nestin Antibody MA1-110 Western Blot
+Western blot analysis of Nestin was performed by loading whole cell lysates (20 µg) of human neural stem cells and HepG2 lysates. Nestin was detected at ~225 kD using MA1-110 at 1:1000 dilution. Actin was used as loading control.
+CPNE7-Induced Autophagy Restores the Physiological Function of Mature Odontoblasts (2021)
+Nestin Antibody (MA1-110) in WB
+Nestin Antibody MA1-110 Western Blot
+Western blot of SH-SY5Y cell lysate showing a band at ~250 kDa using MA1-110 at 1:100 dilution.
+We don't have publications for this application yet, but here are some gallery images showing how it's been used.
+Nestin Antibody (MA1-110) in WB
+Nestin Antibody MA1-110 Western Blot
+Western blot showing a 160 kDa band corresponding to Nestin in neural stem cells and neurons differentiated from iPSC using MA1-110 at 1:1000 dilution.
+We don't have publications for this application yet, but here are some gallery images showing how it's been used.
+Nestin Antibody (MA1-110) in WB
+Nestin Antibody MA1-110 Western Blot
+Western blot showing a 177 kDa band corresponding to Nestin in neural stem cells and neurons differentiated from H9-ESC using MA1-110 at 1:4000 dilution.
+We don't have publications for this application yet, but here are some gallery images showing how it's been used.
+If you need information on other related products or specific protocols, please let me know.
+Sources:
+CPNE7-Induced Autophagy Restores the Physiological Function of Mature Odontoblasts (2021)
+SIRT1 regulates sphingolipid metabolism and neural differentiation of mouse embryonic stem cells (2021)
+EGF signaling promotes the lineage conversion of astrocytes into oligodendrocytes (2022)
+Regulatory Mechanism between Ferritin and Mitochondrial Reactive Oxygen Species (2023)
+Human cytomegalovirus infection perturbs neural progenitor cell fate (2023)
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy (2023)</t>
+  </si>
+  <si>
+    <t>Give Feedback
+Do you have contact us info?
+Sorry! we are unable to provide the requested information. Please contact our customer support team or click the red chat icon on that page for further assistance.
+Give Feedback
+What price i can buy this for?
+thinking...
+What price i can buy this for?
+For the most accurate and up-to-date pricing information for product MA1-110, please refer to the product page on our website or contact our customer support team directly. Pricing can vary based on region, quantity, and any ongoing promotions.
+Give Feedback
+Tell me about the Species Reactivity across the different applications
+Species Reactivity of Nestin Antibody (Catalog Number: MA1-110) Across Different Applications
+Application Species Evidence from Publications
+Immunocytochemistry (ICC/IF) C. elegans Multiple studies report use at dilutions around 1:100 to 1:200 (e.g., PubMed IDs 32632336, 36971196, 37097202, 38790197, 39030180).
+Immunocytochemistry (ICC/IF) House mouse Used in several studies at dilutions 1:400 to 1:500 (e.g., PubMed IDs 30425619, 33083240, 35974013).
+Immunocytochemistry (ICC/IF) Human Reported in multiple publications at dilutions 1:100 to 1:250 (e.g., PubMed IDs 33141462, 34045517, 35974013).
+Flow Cytometry Human Used in flow cytometry applications with human samples (e.g., PubMed ID 37996418). Images available demonstrate use in human cell lines.
+Western Blot (WB) Not Applicable (general use) Validated in western blot applications without species restriction; also used with human and mouse samples (e.g., PubMed IDs 37114074, 35508991, 33981704).
+Immunohistochemistry (Paraffin) (IHC (P)) Human, House mouse Reported in human and mouse tissues (e.g., PubMed IDs 27939779, 34884488, 34747065).
+Immunohistochemistry (Frozen) (IHC (F)) C. elegans Used in frozen tissue sections of C. elegans (e.g., PubMed ID 36669750).
+Immunohistochemistry (IHC) Human, House mouse Demonstrated in human and mouse tissues with various dilutions (e.g., PubMed IDs 34884488, 37552395).
+Overall, the Nestin antibody MA1-110 has been validated and cited in publications for use in multiple species including C. elegans, house mouse, and human across a range of applications such as immunocytochemistry, flow cytometry, western blot, and immunohistochemistry (both paraffin and frozen sections).
+Representative Figures
+Nestin Antibody (MA1-110) in ICC/IF (House mouse)
+Nestin Antibody in ICC/IF House mouse
+Nestin Antibody (MA1-110) in ICC/IF (Human)
+Nestin Antibody in ICC/IF Human
+Nestin Antibody (MA1-110) in Flow Cytometry
+Nestin Antibody in Flow Cytometry
+Nestin Antibody (MA1-110) in Western Blot
+Nestin Antibody in Western Blot
+Nestin Antibody (MA1-110) in IHC (Human Tonsil)
+Nestin Antibody in IHC Human Tonsil
+Sources:
+Publication citing use in C. elegans ICC/IF
+Publication citing use in house mouse ICC/IF
+Publication citing use in human ICC/IF
+Publication citing use in human flow cytometry
+Publication citing use in western blot
+Publication citing use in human and mouse IHC
+Publication citing use in C. elegans IHC (frozen)</t>
+  </si>
+  <si>
+    <t>Species Reactivity for Nestin Antibody (Catalog Number: MA1-110)
+This product has been cited and validated for use in the following species based on publication data:
+Species	Applications Reported
+C. elegans	Immunocytochemistry, Immunohistochemistry (Frozen)
+House mouse (Mus musculus)	Immunocytochemistry, Immunohistochemistry (Paraffin), Western Blot
+Human (Homo sapiens)	Immunocytochemistry, Immunohistochemistry (Paraffin), Flow Cytometry, Western Blot
+Not Applicable / General	Western Blot, Immunocytochemistry (used in unspecified species or cell lines)
+These species cover a range of applications including ICC/IF, IHC (paraffin and frozen), flow cytometry, and western blot, demonstrating the antibody's versatility across model organisms and human samples.
+Sources:
+Publication citing use in C. elegans
+Publication citing use in house mouse
+Publication citing use in human
+Additional publications covering multiple species and applications</t>
+  </si>
+  <si>
+    <t>Latest Publications on Nestin Antibody (Catalog Number: MA1-110)
+PubMed ID	Application	Species	Notes
+37114074	Western Blot, Immunocytochemistry	Not Applicable	Recent validation in western blot and ICC applications.
+35974013	Immunocytochemistry	Human, House mouse	Study on Parkinson's disease models using this antibody.
+34045517	Immunocytochemistry	Human	High-throughput isoform expression analysis.
+34884488	Immunohistochemistry	House mouse	Tissue staining validation.
+33083240	Immunocytochemistry	House mouse	Cellular localization studies.
+33841129	Immunocytochemistry	Human	Cellular expression analysis.
+These publications represent recent research across various journals demonstrating the use of Nestin antibody MA1-110 in applications such as immunocytochemistry, immunohistochemistry, and western blot in human, mouse, and general species contexts.</t>
+  </si>
+  <si>
+    <t>Publications Using Both Immunohistochemistry (IHC) and Western Blot (WB) for Stem Cell Studies with MA1-110
+Publication	Summary
+3D Visualization of Dynamic Cellular Reaction of Pulpal CD11c+ Dendritic Cells against Pulpitis in Whole Murine Tooth (2021)	Used MA1-110 in immunohistochemistry to analyze pulpal immune cells in mouse tooth. Stem cell-related markers were part of the cellular analysis.
+Refining the Role of Pyruvate Dehydrogenase Kinases in Glioblastoma Development (2022)	Applied MA1-110 in both IHC and WB to study stem-like spheroids derived from glioblastoma, focusing on metabolic regulation and stem cell characteristics.
+Mammalian CDC14 phosphatases control exit from stemness in pluripotent cells (2023)	Used MA1-110 in IHC to study neural differentiation and stemness regulation in mouse pluripotent cells.
+Stem cell phenotype predicts therapeutic response in glioblastomas with MGMT promoter methylation (2022)	MA1-110 was used in IHC to evaluate stem cell markers in human glioblastoma samples, correlating with clinical outcomes.
+Deletion of TRPC6, an Autism Risk Gene, Induces Hyperexcitability in Cortical Neurons Derived from Human Pluripotent Stem Cells (2023)	MA1-110 was used in IHC to study neural stem cells derived from human pluripotent stem cells in the context of autism spectrum disorder.
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy (2023)	Used MA1-110 in WB and immunocytochemistry to study glioma stem-like cells and therapeutic resistance mechanisms.
+Representative Figures
+Nestin Antibody (MA1-110) in IHC - Mouse Tooth
+Nestin Antibody MA1-110 IHC Mouse Tooth
+Figure legend: CD11c+ cell at dentin-pulp interface does not express odontoblast differentiation markers DMP1 and Nestin. Immunostaining in mouse tooth showing Nestin (red) and CD11c (green).
+3D Visualization of Dynamic Cellular Reaction of Pulpal CD11c+ Dendritic Cells (2021)
+Nestin Antibody (MA1-110) in WB - Human Neural Stem Cells
+Nestin Antibody MA1-110 Western Blot
+Western blot showing Nestin expression (~225 kDa) in human neural stem cells and HepG2 lysates using MA1-110.
+Nestin Antibody (MA1-110) in WB and ICC - Glioma Stem Cells
+Nestin Antibody MA1-110 WB and ICC
+Figure legend: Western blot and immunofluorescence staining showing reduction of stemness markers including Nestin in glioma stem cells after treatment.
+oHSV-P10 reduces glioma stem cell enrichment (2023)
+If you need more detailed information or additional publications, please let me know.
+Sources:
+3D Visualization of Dynamic Cellular Reaction of Pulpal CD11c+ Dendritic Cells (2021)
+Refining the Role of Pyruvate Dehydrogenase Kinases in Glioblastoma Development (2022)
+Mammalian CDC14 phosphatases control exit from stemness in pluripotent cells (2023)
+Stem cell phenotype predicts therapeutic response in glioblastomas (2022)
+Deletion of TRPC6 induces hyperexcitability in cortical neurons derived from human pluripotent stem cells (2023)
+oHSV-P10 reduces glioma stem cell enrichment after oncolytic HSV therapy (2023)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2735,12 +3182,6 @@
       <sz val="12"/>
       <color rgb="FF3B3B3B"/>
       <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF1B1B1D"/>
-      <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
     <font>
@@ -3085,7 +3526,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3116,39 +3557,120 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3160,94 +3682,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3592,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C1" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3603,10 +4047,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3621,12 +4065,12 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3641,8 +4085,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B9B0AB-1BC4-A343-B126-AE2290BE5A10}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="39.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -3657,24 +4104,167 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="404">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>241</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="409.6">
+      <c r="A4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="409.6">
+      <c r="A5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="409.6">
+      <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="409.6">
+      <c r="A7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="409.6">
+      <c r="A8" t="s">
+        <v>326</v>
+      </c>
+      <c r="B8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="409.6">
+      <c r="A9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="409.6">
+      <c r="A10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="409.6">
+      <c r="A11" t="s">
+        <v>329</v>
+      </c>
+      <c r="B11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="409.6">
+      <c r="A12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="409.6">
+      <c r="A13" t="s">
+        <v>331</v>
+      </c>
+      <c r="B13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="409.6">
+      <c r="A14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B15" t="s">
+        <v>333</v>
+      </c>
+      <c r="C15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="409.6">
+      <c r="A16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -3780,10 +4370,10 @@
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="86" thickBot="1">
@@ -3952,7 +4542,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="409.6" thickBot="1">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>53</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -4066,7 +4656,7 @@
         <v>77</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
         <v>79</v>
@@ -4088,7 +4678,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
         <v>81</v>
@@ -4173,211 +4763,211 @@
     </row>
     <row r="45" spans="1:3" ht="154" thickBot="1">
       <c r="A45" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C45" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="86" thickBot="1">
       <c r="A46" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B46" s="2">
         <v>4469605</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="239" thickBot="1">
       <c r="A47" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B47" s="2">
         <v>75009240</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="137" thickBot="1">
       <c r="A48" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="137" thickBot="1">
       <c r="A49" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B49" s="4">
         <v>12579017</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="103" thickBot="1">
       <c r="A50" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="18" thickBot="1">
       <c r="A51" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B51" s="4">
         <v>34577</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="389" thickBot="1">
       <c r="A52" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="69" thickBot="1">
       <c r="A53" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="103" thickBot="1">
       <c r="A54" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="52" thickBot="1">
       <c r="A55" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" t="s">
         <v>129</v>
-      </c>
-      <c r="C55" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="86" thickBot="1">
       <c r="A56" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="154" thickBot="1">
       <c r="A57" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="69" thickBot="1">
       <c r="A58" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="86" thickBot="1">
       <c r="A59" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="154" thickBot="1">
       <c r="A60" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C60" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="103" thickBot="1">
       <c r="A61" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="86" thickBot="1">
       <c r="A62" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C62" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="119">
       <c r="A63" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -4402,54 +4992,54 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="35" thickBot="1">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="60" t="s">
+      <c r="B2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="69" thickBot="1">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="60" t="s">
+      <c r="B3" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="103" thickBot="1">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="60" t="s">
+      <c r="B4" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="35" thickBot="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="60" t="s">
+      <c r="B5" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="29" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -4457,109 +5047,109 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="52" thickBot="1">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="60" t="s">
+      <c r="B7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="69" thickBot="1">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="60" t="s">
+      <c r="B8" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="86" thickBot="1">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="60" t="s">
+      <c r="B9" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="69" thickBot="1">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="60" t="s">
+      <c r="B10" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="52" thickBot="1">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="60" t="s">
+      <c r="B11" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="69" thickBot="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="60" t="s">
+      <c r="B12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" thickBot="1">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="52" thickBot="1">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="60" t="s">
+      <c r="B14" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="103" thickBot="1">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="60" t="s">
+      <c r="B15" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="103" thickBot="1">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="29" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
@@ -4567,10 +5157,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="86" thickBot="1">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="25" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -4578,21 +5168,21 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="35" thickBot="1">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="60" t="s">
+      <c r="B18" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18" thickBot="1">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="27" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -4600,24 +5190,24 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="69" thickBot="1">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="60" t="s">
+      <c r="B20" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="103" thickBot="1">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="60" t="s">
+      <c r="B21" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4634,7 +5224,7 @@
       <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3" ht="17" thickBot="1">
-      <c r="A25" s="15"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
     </row>
@@ -4823,7 +5413,7 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="137" thickBot="1">
@@ -4837,7 +5427,7 @@
         <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="188" thickBot="1">
@@ -4851,7 +5441,7 @@
         <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17" thickBot="1">
@@ -4939,7 +5529,7 @@
       <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3" ht="17" thickBot="1">
-      <c r="A25" s="15"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
     </row>
@@ -5122,6 +5712,147 @@
     <row r="70" spans="1:2">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB8EAD79-CE11-9447-A6FB-85EB804FBAE4}">
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="135.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="B44" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5135,63 +5866,63 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="E1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F1" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="G1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="F3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="E5" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -5205,428 +5936,428 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:10" ht="32">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="J1" s="22" t="s">
+      <c r="C1" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="170">
+      <c r="A2" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="409.6">
+      <c r="A3" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="409.6">
+      <c r="A4" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="238">
+      <c r="A5" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="255">
+      <c r="A6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="409.6">
+      <c r="A7" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="170">
-      <c r="A2" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2" s="19" t="s">
+    <row r="8" spans="1:10" ht="409.6">
+      <c r="A8" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="409.6">
-      <c r="A3" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="C8" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="409.6">
+      <c r="A9" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="409.6">
-      <c r="A4" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="C9" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="409.6">
+      <c r="A10" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="238">
-      <c r="A5" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="C10" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="409.6">
+      <c r="A11" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="255">
-      <c r="A6" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="409.6">
-      <c r="A7" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="409.6">
-      <c r="A8" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="409.6">
-      <c r="A9" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="409.6">
-      <c r="A10" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="409.6">
-      <c r="A11" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>251</v>
+      <c r="C11" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="409.6">
-      <c r="A12" s="18" t="s">
-        <v>207</v>
+      <c r="A12" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>252</v>
+      <c r="C12" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="409.6">
-      <c r="A13" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="A13" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="19">
         <v>11012044</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>253</v>
+      <c r="C13" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="409.6">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>254</v>
+      <c r="B14" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="409.6">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>255</v>
+      <c r="B15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="409.6">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>256</v>
+      <c r="B16" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="409.6">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>257</v>
+      <c r="B17" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="409.6">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>248</v>
+      <c r="B18" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="409.6">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>258</v>
+      <c r="B19" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="409.6">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>259</v>
+      <c r="B20" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="409.6">
-      <c r="A21" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>260</v>
+      <c r="A21" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="409.6">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>261</v>
+      <c r="B22" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="409.6">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>87</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>262</v>
+      <c r="C23" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="409.6">
-      <c r="A24" s="18" t="s">
-        <v>136</v>
+      <c r="A24" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>263</v>
+        <v>232</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="409.6">
-      <c r="A25" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>264</v>
+      <c r="A25" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5654,1589 +6385,1650 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="128" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="96" customHeight="1">
+      <c r="A3" s="37"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="59"/>
+    </row>
+    <row r="4" spans="1:3" ht="160" customHeight="1">
+      <c r="A4" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="37"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="61"/>
+    </row>
+    <row r="6" spans="1:3" ht="224" customHeight="1">
+      <c r="A6" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="37"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="61"/>
+    </row>
+    <row r="8" spans="1:3" ht="64" customHeight="1">
+      <c r="A8" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="30" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="335" customHeight="1">
+      <c r="A9" s="39"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="63"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="39"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="63"/>
+    </row>
+    <row r="11" spans="1:3" ht="320" customHeight="1">
+      <c r="A11" s="39"/>
+      <c r="B11" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="96" customHeight="1">
-      <c r="A3" s="35"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="37"/>
-    </row>
-    <row r="4" spans="1:3" ht="160" customHeight="1">
-      <c r="A4" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="30" t="s">
+      <c r="C11" s="63"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="64"/>
+    </row>
+    <row r="13" spans="1:3" ht="272" customHeight="1">
+      <c r="A13" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="38"/>
+      <c r="C13" s="62" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="39"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="63"/>
+    </row>
+    <row r="15" spans="1:3" ht="112" customHeight="1">
+      <c r="A15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="63"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="63"/>
+    </row>
+    <row r="17" spans="1:3" ht="48" customHeight="1">
+      <c r="A17" s="39"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="63"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="39"/>
+      <c r="B18" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="35"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="39"/>
-    </row>
-    <row r="6" spans="1:3" ht="224" customHeight="1">
-      <c r="A6" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="30" t="s">
+      <c r="C18" s="63"/>
+    </row>
+    <row r="19" spans="1:3" ht="32" customHeight="1">
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="64"/>
+    </row>
+    <row r="20" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A20" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="62" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="63"/>
+    </row>
+    <row r="22" spans="1:3" ht="32" customHeight="1">
+      <c r="A22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="63"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="39"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="63"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="39"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="63"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="39"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="63"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="39"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="63"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="39"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="63"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="39"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="63"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="39"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="63"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="39"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="63"/>
+    </row>
+    <row r="31" spans="1:3" ht="80" customHeight="1">
+      <c r="A31" s="39"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="63"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="39"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="63"/>
+    </row>
+    <row r="33" spans="1:3" ht="64" customHeight="1">
+      <c r="A33" s="39"/>
+      <c r="B33" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="35"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="39"/>
-    </row>
-    <row r="8" spans="1:3" ht="64" customHeight="1">
-      <c r="A8" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="27" t="s">
+      <c r="C33" s="63"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="64"/>
+    </row>
+    <row r="35" spans="1:3" ht="306" customHeight="1">
+      <c r="A35" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="38"/>
+      <c r="C35" s="62" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="39"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="63"/>
+    </row>
+    <row r="37" spans="1:3" ht="32" customHeight="1">
+      <c r="A37" s="39"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="63"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="39"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="63"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="39"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="63"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="39"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="63"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="39"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="63"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="39"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="63"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="39"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="63"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="39"/>
+      <c r="B44" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="63"/>
+    </row>
+    <row r="45" spans="1:3" ht="64" customHeight="1">
+      <c r="A45" s="37"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="64"/>
+    </row>
+    <row r="46" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A46" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="38"/>
+      <c r="C46" s="62" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="64" customHeight="1">
+      <c r="A47" s="39"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="63"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="39"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="63"/>
+    </row>
+    <row r="49" spans="1:3" ht="48" customHeight="1">
+      <c r="A49" s="39"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="63"/>
+    </row>
+    <row r="50" spans="1:3" ht="48" customHeight="1">
+      <c r="A50" s="39"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="63"/>
+    </row>
+    <row r="51" spans="1:3" ht="32" customHeight="1">
+      <c r="A51" s="39"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="63"/>
+    </row>
+    <row r="52" spans="1:3" ht="48" customHeight="1">
+      <c r="A52" s="39"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="63"/>
+    </row>
+    <row r="53" spans="1:3" ht="48" customHeight="1">
+      <c r="A53" s="39"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="63"/>
+    </row>
+    <row r="54" spans="1:3" ht="32" customHeight="1">
+      <c r="A54" s="39"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="63"/>
+    </row>
+    <row r="55" spans="1:3" ht="64" customHeight="1">
+      <c r="A55" s="39"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="63"/>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="39"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="63"/>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="39"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="63"/>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="39"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="63"/>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="39"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="63"/>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="39"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="63"/>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="39"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="63"/>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="39"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="63"/>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="39"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="63"/>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="39"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="63"/>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="39"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="63"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="39"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="63"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="39"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="63"/>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="39"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="63"/>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="39"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="63"/>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="39"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="63"/>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="39"/>
+      <c r="B71" s="35"/>
+      <c r="C71" s="63"/>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="39"/>
+      <c r="B72" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72" s="63"/>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="37"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="64"/>
+    </row>
+    <row r="74" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A74" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" s="38"/>
+      <c r="C74" s="62" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="80" customHeight="1">
+      <c r="A75" s="39"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="63"/>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="39"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="63"/>
+    </row>
+    <row r="77" spans="1:3" ht="48" customHeight="1">
+      <c r="A77" s="39"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="63"/>
+    </row>
+    <row r="78" spans="1:3" ht="48" customHeight="1">
+      <c r="A78" s="39"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="63"/>
+    </row>
+    <row r="79" spans="1:3" ht="48" customHeight="1">
+      <c r="A79" s="39"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="63"/>
+    </row>
+    <row r="80" spans="1:3" ht="32" customHeight="1">
+      <c r="A80" s="39"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="63"/>
+    </row>
+    <row r="81" spans="1:3" ht="64" customHeight="1">
+      <c r="A81" s="39"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="63"/>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="39"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="63"/>
+    </row>
+    <row r="83" spans="1:3" ht="32" customHeight="1">
+      <c r="A83" s="39"/>
+      <c r="B83" s="38"/>
+      <c r="C83" s="63"/>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="39"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="63"/>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="39"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="63"/>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="39"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="63"/>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="39"/>
+      <c r="B87" s="38"/>
+      <c r="C87" s="63"/>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="39"/>
+      <c r="B88" s="38"/>
+      <c r="C88" s="63"/>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="39"/>
+      <c r="B89" s="38"/>
+      <c r="C89" s="63"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="39"/>
+      <c r="B90" s="38"/>
+      <c r="C90" s="63"/>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="39"/>
+      <c r="B91" s="38"/>
+      <c r="C91" s="63"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="39"/>
+      <c r="B92" s="38"/>
+      <c r="C92" s="63"/>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="39"/>
+      <c r="B93" s="38"/>
+      <c r="C93" s="63"/>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="39"/>
+      <c r="B94" s="38"/>
+      <c r="C94" s="63"/>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="39"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="63"/>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="39"/>
+      <c r="B96" s="38"/>
+      <c r="C96" s="63"/>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="39"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="63"/>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="39"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="63"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="39"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="63"/>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="39"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="63"/>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="39"/>
+      <c r="B101" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C101" s="63"/>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="37"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="64"/>
+    </row>
+    <row r="103" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A103" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="B103" s="38"/>
+      <c r="C103" s="62" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="80" customHeight="1">
+      <c r="A104" s="39"/>
+      <c r="B104" s="38"/>
+      <c r="C104" s="63"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="39"/>
+      <c r="B105" s="38"/>
+      <c r="C105" s="63"/>
+    </row>
+    <row r="106" spans="1:3" ht="64" customHeight="1">
+      <c r="A106" s="39"/>
+      <c r="B106" s="38"/>
+      <c r="C106" s="63"/>
+    </row>
+    <row r="107" spans="1:3" ht="64" customHeight="1">
+      <c r="A107" s="39"/>
+      <c r="B107" s="38"/>
+      <c r="C107" s="63"/>
+    </row>
+    <row r="108" spans="1:3" ht="48" customHeight="1">
+      <c r="A108" s="39"/>
+      <c r="B108" s="38"/>
+      <c r="C108" s="63"/>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="39"/>
+      <c r="B109" s="38"/>
+      <c r="C109" s="63"/>
+    </row>
+    <row r="110" spans="1:3" ht="32" customHeight="1">
+      <c r="A110" s="39"/>
+      <c r="B110" s="38"/>
+      <c r="C110" s="63"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="39"/>
+      <c r="B111" s="38"/>
+      <c r="C111" s="63"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="39"/>
+      <c r="B112" s="38"/>
+      <c r="C112" s="63"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="39"/>
+      <c r="B113" s="38"/>
+      <c r="C113" s="63"/>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="39"/>
+      <c r="B114" s="38"/>
+      <c r="C114" s="63"/>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="39"/>
+      <c r="B115" s="38"/>
+      <c r="C115" s="63"/>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="39"/>
+      <c r="B116" s="38"/>
+      <c r="C116" s="63"/>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="39"/>
+      <c r="B117" s="38"/>
+      <c r="C117" s="63"/>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="39"/>
+      <c r="B118" s="38"/>
+      <c r="C118" s="63"/>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="39"/>
+      <c r="B119" s="38"/>
+      <c r="C119" s="63"/>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="39"/>
+      <c r="B120" s="38"/>
+      <c r="C120" s="63"/>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="39"/>
+      <c r="B121" s="38"/>
+      <c r="C121" s="63"/>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="39"/>
+      <c r="B122" s="38"/>
+      <c r="C122" s="63"/>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="39"/>
+      <c r="B123" s="38"/>
+      <c r="C123" s="63"/>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="39"/>
+      <c r="B124" s="38"/>
+      <c r="C124" s="63"/>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="39"/>
+      <c r="B125" s="38"/>
+      <c r="C125" s="63"/>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="39"/>
+      <c r="B126" s="35"/>
+      <c r="C126" s="63"/>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="39"/>
+      <c r="B127" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C127" s="63"/>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="37"/>
+      <c r="B128" s="38"/>
+      <c r="C128" s="64"/>
+    </row>
+    <row r="129" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A129" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="B129" s="38"/>
+      <c r="C129" s="62" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="80" customHeight="1">
+      <c r="A130" s="39"/>
+      <c r="B130" s="38"/>
+      <c r="C130" s="63"/>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="39"/>
+      <c r="B131" s="38"/>
+      <c r="C131" s="63"/>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="39"/>
+      <c r="B132" s="38"/>
+      <c r="C132" s="63"/>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="39"/>
+      <c r="B133" s="38"/>
+      <c r="C133" s="63"/>
+    </row>
+    <row r="134" spans="1:3" ht="48" customHeight="1">
+      <c r="A134" s="39"/>
+      <c r="B134" s="38"/>
+      <c r="C134" s="63"/>
+    </row>
+    <row r="135" spans="1:3" ht="80" customHeight="1">
+      <c r="A135" s="39"/>
+      <c r="B135" s="38"/>
+      <c r="C135" s="63"/>
+    </row>
+    <row r="136" spans="1:3" ht="64" customHeight="1">
+      <c r="A136" s="39"/>
+      <c r="B136" s="38"/>
+      <c r="C136" s="63"/>
+    </row>
+    <row r="137" spans="1:3" ht="32" customHeight="1">
+      <c r="A137" s="39"/>
+      <c r="B137" s="38"/>
+      <c r="C137" s="63"/>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="39"/>
+      <c r="B138" s="38"/>
+      <c r="C138" s="63"/>
+    </row>
+    <row r="139" spans="1:3" ht="80" customHeight="1">
+      <c r="A139" s="39"/>
+      <c r="B139" s="35"/>
+      <c r="C139" s="63"/>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="39"/>
+      <c r="B140" s="55">
+        <v>11012044</v>
+      </c>
+      <c r="C140" s="63"/>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="37"/>
+      <c r="B141" s="56"/>
+      <c r="C141" s="64"/>
+    </row>
+    <row r="142" spans="1:3" ht="404" customHeight="1">
+      <c r="A142" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B142" s="56"/>
+      <c r="C142" s="62" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="64" customHeight="1">
+      <c r="A143" s="39"/>
+      <c r="B143" s="56"/>
+      <c r="C143" s="63"/>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="39"/>
+      <c r="B144" s="56"/>
+      <c r="C144" s="63"/>
+    </row>
+    <row r="145" spans="1:3" ht="64" customHeight="1">
+      <c r="A145" s="39"/>
+      <c r="B145" s="56"/>
+      <c r="C145" s="63"/>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="39"/>
+      <c r="B146" s="56"/>
+      <c r="C146" s="63"/>
+    </row>
+    <row r="147" spans="1:3" ht="32" customHeight="1">
+      <c r="A147" s="39"/>
+      <c r="B147" s="56"/>
+      <c r="C147" s="63"/>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="39"/>
+      <c r="B148" s="56"/>
+      <c r="C148" s="63"/>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="39"/>
+      <c r="B149" s="56"/>
+      <c r="C149" s="63"/>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="39"/>
+      <c r="B150" s="56"/>
+      <c r="C150" s="63"/>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="39"/>
+      <c r="B151" s="56"/>
+      <c r="C151" s="63"/>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="39"/>
+      <c r="B152" s="56"/>
+      <c r="C152" s="63"/>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="39"/>
+      <c r="B153" s="56"/>
+      <c r="C153" s="63"/>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="39"/>
+      <c r="B154" s="56"/>
+      <c r="C154" s="63"/>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="39"/>
+      <c r="B155" s="57"/>
+      <c r="C155" s="63"/>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="39"/>
+      <c r="B156" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C156" s="63"/>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="37"/>
+      <c r="B157" s="38"/>
+      <c r="C157" s="64"/>
+    </row>
+    <row r="158" spans="1:3" ht="68" customHeight="1">
+      <c r="A158" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B158" s="35"/>
+      <c r="C158" s="62" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="32" customHeight="1">
+      <c r="A159" s="39"/>
+      <c r="B159" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C159" s="63"/>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="37"/>
+      <c r="B160" s="35"/>
+      <c r="C160" s="64"/>
+    </row>
+    <row r="161" spans="1:3" ht="32" customHeight="1">
+      <c r="A161" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B161" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C161" s="65" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="46"/>
+      <c r="B162" s="38"/>
+      <c r="C162" s="66"/>
+    </row>
+    <row r="163" spans="1:3" ht="221" customHeight="1">
+      <c r="A163" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B163" s="38"/>
+      <c r="C163" s="62" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="48" customHeight="1">
+      <c r="A164" s="39"/>
+      <c r="B164" s="38"/>
+      <c r="C164" s="63"/>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="39"/>
+      <c r="B165" s="38"/>
+      <c r="C165" s="63"/>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="39"/>
+      <c r="B166" s="38"/>
+      <c r="C166" s="63"/>
+    </row>
+    <row r="167" spans="1:3" ht="32" customHeight="1">
+      <c r="A167" s="39"/>
+      <c r="B167" s="38"/>
+      <c r="C167" s="63"/>
+    </row>
+    <row r="168" spans="1:3" ht="32" customHeight="1">
+      <c r="A168" s="39"/>
+      <c r="B168" s="38"/>
+      <c r="C168" s="63"/>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="39"/>
+      <c r="B169" s="38"/>
+      <c r="C169" s="63"/>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="39"/>
+      <c r="B170" s="35"/>
+      <c r="C170" s="63"/>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="39"/>
+      <c r="B171" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C171" s="63"/>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" s="37"/>
+      <c r="B172" s="38"/>
+      <c r="C172" s="64"/>
+    </row>
+    <row r="173" spans="1:3" ht="238" customHeight="1">
+      <c r="A173" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B173" s="38"/>
+      <c r="C173" s="62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="32" customHeight="1">
+      <c r="A174" s="43"/>
+      <c r="B174" s="38"/>
+      <c r="C174" s="63"/>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="43"/>
+      <c r="B175" s="38"/>
+      <c r="C175" s="63"/>
+    </row>
+    <row r="176" spans="1:3" ht="32" customHeight="1">
+      <c r="A176" s="43"/>
+      <c r="B176" s="38"/>
+      <c r="C176" s="63"/>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" s="43"/>
+      <c r="B177" s="35"/>
+      <c r="C177" s="63"/>
+    </row>
+    <row r="178" spans="1:3" ht="64" customHeight="1">
+      <c r="A178" s="43"/>
+      <c r="B178" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C178" s="63"/>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="44"/>
+      <c r="B179" s="38"/>
+      <c r="C179" s="64"/>
+    </row>
+    <row r="180" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A180" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B180" s="38"/>
+      <c r="C180" s="62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="48" customHeight="1">
+      <c r="A181" s="39"/>
+      <c r="B181" s="38"/>
+      <c r="C181" s="63"/>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="39"/>
+      <c r="B182" s="38"/>
+      <c r="C182" s="63"/>
+    </row>
+    <row r="183" spans="1:3" ht="64" customHeight="1">
+      <c r="A183" s="39"/>
+      <c r="B183" s="38"/>
+      <c r="C183" s="63"/>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="39"/>
+      <c r="B184" s="38"/>
+      <c r="C184" s="63"/>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" s="39"/>
+      <c r="B185" s="38"/>
+      <c r="C185" s="63"/>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" s="39"/>
+      <c r="B186" s="38"/>
+      <c r="C186" s="63"/>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" s="39"/>
+      <c r="B187" s="38"/>
+      <c r="C187" s="63"/>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" s="39"/>
+      <c r="B188" s="38"/>
+      <c r="C188" s="63"/>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" s="39"/>
+      <c r="B189" s="38"/>
+      <c r="C189" s="63"/>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" s="39"/>
+      <c r="B190" s="38"/>
+      <c r="C190" s="63"/>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" s="39"/>
+      <c r="B191" s="38"/>
+      <c r="C191" s="63"/>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" s="39"/>
+      <c r="B192" s="38"/>
+      <c r="C192" s="63"/>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" s="39"/>
+      <c r="B193" s="38"/>
+      <c r="C193" s="63"/>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" s="39"/>
+      <c r="B194" s="38"/>
+      <c r="C194" s="63"/>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" s="39"/>
+      <c r="B195" s="38"/>
+      <c r="C195" s="63"/>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" s="39"/>
+      <c r="B196" s="38"/>
+      <c r="C196" s="63"/>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" s="39"/>
+      <c r="B197" s="38"/>
+      <c r="C197" s="63"/>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" s="39"/>
+      <c r="B198" s="38"/>
+      <c r="C198" s="63"/>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" s="39"/>
+      <c r="B199" s="35"/>
+      <c r="C199" s="63"/>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" s="39"/>
+      <c r="B200" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C200" s="63"/>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" s="37"/>
+      <c r="B201" s="35"/>
+      <c r="C201" s="64"/>
+    </row>
+    <row r="202" spans="1:3" ht="48" customHeight="1">
+      <c r="A202" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B202" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202" s="65" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" s="37"/>
+      <c r="B203" s="38"/>
+      <c r="C203" s="66"/>
+    </row>
+    <row r="204" spans="1:3" ht="255" customHeight="1">
+      <c r="A204" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B204" s="38"/>
+      <c r="C204" s="62" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="96" customHeight="1">
+      <c r="A205" s="39"/>
+      <c r="B205" s="38"/>
+      <c r="C205" s="63"/>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" s="39"/>
+      <c r="B206" s="38"/>
+      <c r="C206" s="63"/>
+    </row>
+    <row r="207" spans="1:3" ht="32" customHeight="1">
+      <c r="A207" s="39"/>
+      <c r="B207" s="38"/>
+      <c r="C207" s="63"/>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" s="39"/>
+      <c r="B208" s="38"/>
+      <c r="C208" s="63"/>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" s="39"/>
+      <c r="B209" s="35"/>
+      <c r="C209" s="63"/>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" s="39"/>
+      <c r="B210" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C210" s="63"/>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" s="37"/>
+      <c r="B211" s="38"/>
+      <c r="C211" s="64"/>
+    </row>
+    <row r="212" spans="1:3" ht="255" customHeight="1">
+      <c r="A212" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B212" s="38"/>
+      <c r="C212" s="62" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="335" customHeight="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="28"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="28"/>
-    </row>
-    <row r="11" spans="1:3" ht="320" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="28"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="35"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="29"/>
-    </row>
-    <row r="13" spans="1:3" ht="272" customHeight="1">
-      <c r="A13" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="27" t="s">
+    <row r="213" spans="1:3">
+      <c r="A213" s="39"/>
+      <c r="B213" s="38"/>
+      <c r="C213" s="63"/>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" s="39"/>
+      <c r="B214" s="38"/>
+      <c r="C214" s="63"/>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" s="39"/>
+      <c r="B215" s="38"/>
+      <c r="C215" s="63"/>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216" s="39"/>
+      <c r="B216" s="38"/>
+      <c r="C216" s="63"/>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" s="39"/>
+      <c r="B217" s="38"/>
+      <c r="C217" s="63"/>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" s="39"/>
+      <c r="B218" s="38"/>
+      <c r="C218" s="63"/>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" s="39"/>
+      <c r="B219" s="38"/>
+      <c r="C219" s="63"/>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" s="39"/>
+      <c r="B220" s="38"/>
+      <c r="C220" s="63"/>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" s="39"/>
+      <c r="B221" s="35"/>
+      <c r="C221" s="63"/>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" s="39"/>
+      <c r="B222" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C222" s="63"/>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" s="37"/>
+      <c r="B223" s="38"/>
+      <c r="C223" s="64"/>
+    </row>
+    <row r="224" spans="1:3" ht="102" customHeight="1">
+      <c r="A224" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B224" s="38"/>
+      <c r="C224" s="62" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="34"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="28"/>
-    </row>
-    <row r="15" spans="1:3" ht="112" customHeight="1">
-      <c r="A15" s="34"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="28"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="34"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="28"/>
-    </row>
-    <row r="17" spans="1:3" ht="48" customHeight="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="28"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="34"/>
-      <c r="B18" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="28"/>
-    </row>
-    <row r="19" spans="1:3" ht="32" customHeight="1">
-      <c r="A19" s="35"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="29"/>
-    </row>
-    <row r="20" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A20" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="27" t="s">
+    <row r="225" spans="1:3" ht="48" customHeight="1">
+      <c r="A225" s="39"/>
+      <c r="B225" s="35"/>
+      <c r="C225" s="63"/>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" s="39"/>
+      <c r="B226" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C226" s="63"/>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" s="37"/>
+      <c r="B227" s="38"/>
+      <c r="C227" s="64"/>
+    </row>
+    <row r="228" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A228" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B228" s="38"/>
+      <c r="C228" s="62" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="32" customHeight="1">
+      <c r="A229" s="39"/>
+      <c r="B229" s="38"/>
+      <c r="C229" s="63"/>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" s="39"/>
+      <c r="B230" s="38"/>
+      <c r="C230" s="63"/>
+    </row>
+    <row r="231" spans="1:3" ht="48" customHeight="1">
+      <c r="A231" s="39"/>
+      <c r="B231" s="38"/>
+      <c r="C231" s="63"/>
+    </row>
+    <row r="232" spans="1:3" ht="48" customHeight="1">
+      <c r="A232" s="39"/>
+      <c r="B232" s="38"/>
+      <c r="C232" s="63"/>
+    </row>
+    <row r="233" spans="1:3" ht="64" customHeight="1">
+      <c r="A233" s="39"/>
+      <c r="B233" s="38"/>
+      <c r="C233" s="63"/>
+    </row>
+    <row r="234" spans="1:3" ht="48" customHeight="1">
+      <c r="A234" s="39"/>
+      <c r="B234" s="38"/>
+      <c r="C234" s="63"/>
+    </row>
+    <row r="235" spans="1:3" ht="48" customHeight="1">
+      <c r="A235" s="39"/>
+      <c r="B235" s="38"/>
+      <c r="C235" s="63"/>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" s="39"/>
+      <c r="B236" s="38"/>
+      <c r="C236" s="63"/>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" s="39"/>
+      <c r="B237" s="38"/>
+      <c r="C237" s="63"/>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" s="39"/>
+      <c r="B238" s="38"/>
+      <c r="C238" s="63"/>
+    </row>
+    <row r="239" spans="1:3" ht="32" customHeight="1">
+      <c r="A239" s="39"/>
+      <c r="B239" s="38"/>
+      <c r="C239" s="63"/>
+    </row>
+    <row r="240" spans="1:3" ht="32" customHeight="1">
+      <c r="A240" s="39"/>
+      <c r="B240" s="38"/>
+      <c r="C240" s="63"/>
+    </row>
+    <row r="241" spans="1:3" ht="32" customHeight="1">
+      <c r="A241" s="39"/>
+      <c r="B241" s="38"/>
+      <c r="C241" s="63"/>
+    </row>
+    <row r="242" spans="1:3" ht="32" customHeight="1">
+      <c r="A242" s="39"/>
+      <c r="B242" s="35"/>
+      <c r="C242" s="63"/>
+    </row>
+    <row r="243" spans="1:3" ht="32" customHeight="1">
+      <c r="A243" s="39"/>
+      <c r="B243" s="47">
+        <v>15472</v>
+      </c>
+      <c r="C243" s="63"/>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" s="37"/>
+      <c r="B244" s="48"/>
+      <c r="C244" s="64"/>
+    </row>
+    <row r="245" spans="1:3" ht="289" customHeight="1">
+      <c r="A245" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B245" s="48"/>
+      <c r="C245" s="62" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="34"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="28"/>
-    </row>
-    <row r="22" spans="1:3" ht="32" customHeight="1">
-      <c r="A22" s="34"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="28"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="34"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="28"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="34"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="28"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="34"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="28"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="34"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="28"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="34"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="28"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="34"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="28"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="34"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="28"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="34"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="28"/>
-    </row>
-    <row r="31" spans="1:3" ht="80" customHeight="1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="28"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="34"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="28"/>
-    </row>
-    <row r="33" spans="1:3" ht="64" customHeight="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="28"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="35"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="29"/>
-    </row>
-    <row r="35" spans="1:3" ht="306" customHeight="1">
-      <c r="A35" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="27" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="34"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="28"/>
-    </row>
-    <row r="37" spans="1:3" ht="32" customHeight="1">
-      <c r="A37" s="34"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="28"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="34"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="28"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="34"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="28"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="34"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="28"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="34"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="28"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="34"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="28"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="34"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="28"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="34"/>
-      <c r="B44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="28"/>
-    </row>
-    <row r="45" spans="1:3" ht="64" customHeight="1">
-      <c r="A45" s="35"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="29"/>
-    </row>
-    <row r="46" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A46" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="27" t="s">
+    <row r="246" spans="1:3" ht="80" customHeight="1">
+      <c r="A246" s="51"/>
+      <c r="B246" s="48"/>
+      <c r="C246" s="63"/>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="51"/>
+      <c r="B247" s="48"/>
+      <c r="C247" s="63"/>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="51"/>
+      <c r="B248" s="48"/>
+      <c r="C248" s="63"/>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="51"/>
+      <c r="B249" s="48"/>
+      <c r="C249" s="63"/>
+    </row>
+    <row r="250" spans="1:3" ht="32" customHeight="1">
+      <c r="A250" s="51"/>
+      <c r="B250" s="48"/>
+      <c r="C250" s="63"/>
+    </row>
+    <row r="251" spans="1:3" ht="32" customHeight="1">
+      <c r="A251" s="51"/>
+      <c r="B251" s="48"/>
+      <c r="C251" s="63"/>
+    </row>
+    <row r="252" spans="1:3" ht="32" customHeight="1">
+      <c r="A252" s="51"/>
+      <c r="B252" s="49"/>
+      <c r="C252" s="63"/>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" s="51"/>
+      <c r="B253" s="53">
+        <v>75009240</v>
+      </c>
+      <c r="C253" s="63"/>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" s="52"/>
+      <c r="B254" s="54"/>
+      <c r="C254" s="64"/>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B255" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="C255" s="65" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" s="41"/>
+      <c r="B256" s="38"/>
+      <c r="C256" s="66"/>
+    </row>
+    <row r="257" spans="1:3" ht="388" customHeight="1">
+      <c r="A257" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B257" s="38"/>
+      <c r="C257" s="62" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="64" customHeight="1">
-      <c r="A47" s="34"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="28"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="34"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="28"/>
-    </row>
-    <row r="49" spans="1:3" ht="48" customHeight="1">
-      <c r="A49" s="34"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="28"/>
-    </row>
-    <row r="50" spans="1:3" ht="48" customHeight="1">
-      <c r="A50" s="34"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="28"/>
-    </row>
-    <row r="51" spans="1:3" ht="32" customHeight="1">
-      <c r="A51" s="34"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="28"/>
-    </row>
-    <row r="52" spans="1:3" ht="48" customHeight="1">
-      <c r="A52" s="34"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="28"/>
-    </row>
-    <row r="53" spans="1:3" ht="48" customHeight="1">
-      <c r="A53" s="34"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="28"/>
-    </row>
-    <row r="54" spans="1:3" ht="32" customHeight="1">
-      <c r="A54" s="34"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="28"/>
-    </row>
-    <row r="55" spans="1:3" ht="64" customHeight="1">
-      <c r="A55" s="34"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="28"/>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="34"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="28"/>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="34"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="28"/>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="34"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="28"/>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="34"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="28"/>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="34"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="28"/>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="34"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="28"/>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="34"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="28"/>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="34"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="28"/>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="34"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="28"/>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="34"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="28"/>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="34"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="28"/>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="34"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="28"/>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="34"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="28"/>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="34"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="28"/>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="34"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="28"/>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="34"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="28"/>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="34"/>
-      <c r="B72" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C72" s="28"/>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="35"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="29"/>
-    </row>
-    <row r="74" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A74" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="B74" s="31"/>
-      <c r="C74" s="27" t="s">
+    <row r="258" spans="1:3">
+      <c r="A258" s="39"/>
+      <c r="B258" s="38"/>
+      <c r="C258" s="63"/>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" s="39"/>
+      <c r="B259" s="38"/>
+      <c r="C259" s="63"/>
+    </row>
+    <row r="260" spans="1:3" ht="48" customHeight="1">
+      <c r="A260" s="39"/>
+      <c r="B260" s="38"/>
+      <c r="C260" s="63"/>
+    </row>
+    <row r="261" spans="1:3" ht="32" customHeight="1">
+      <c r="A261" s="39"/>
+      <c r="B261" s="38"/>
+      <c r="C261" s="63"/>
+    </row>
+    <row r="262" spans="1:3" ht="32" customHeight="1">
+      <c r="A262" s="39"/>
+      <c r="B262" s="38"/>
+      <c r="C262" s="63"/>
+    </row>
+    <row r="263" spans="1:3" ht="32" customHeight="1">
+      <c r="A263" s="39"/>
+      <c r="B263" s="38"/>
+      <c r="C263" s="63"/>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" s="39"/>
+      <c r="B264" s="38"/>
+      <c r="C264" s="63"/>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" s="39"/>
+      <c r="B265" s="38"/>
+      <c r="C265" s="63"/>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" s="39"/>
+      <c r="B266" s="38"/>
+      <c r="C266" s="63"/>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" s="39"/>
+      <c r="B267" s="38"/>
+      <c r="C267" s="63"/>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" s="39"/>
+      <c r="B268" s="38"/>
+      <c r="C268" s="63"/>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" s="39"/>
+      <c r="B269" s="38"/>
+      <c r="C269" s="63"/>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" s="39"/>
+      <c r="B270" s="35"/>
+      <c r="C270" s="63"/>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" s="39"/>
+      <c r="B271" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C271" s="63"/>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" s="37"/>
+      <c r="B272" s="38"/>
+      <c r="C272" s="64"/>
+    </row>
+    <row r="273" spans="1:3" ht="306" customHeight="1">
+      <c r="A273" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B273" s="38"/>
+      <c r="C273" s="62" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="80" customHeight="1">
-      <c r="A75" s="34"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="28"/>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="34"/>
-      <c r="B76" s="31"/>
-      <c r="C76" s="28"/>
-    </row>
-    <row r="77" spans="1:3" ht="48" customHeight="1">
-      <c r="A77" s="34"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="28"/>
-    </row>
-    <row r="78" spans="1:3" ht="48" customHeight="1">
-      <c r="A78" s="34"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="28"/>
-    </row>
-    <row r="79" spans="1:3" ht="48" customHeight="1">
-      <c r="A79" s="34"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="28"/>
-    </row>
-    <row r="80" spans="1:3" ht="32" customHeight="1">
-      <c r="A80" s="34"/>
-      <c r="B80" s="31"/>
-      <c r="C80" s="28"/>
-    </row>
-    <row r="81" spans="1:3" ht="64" customHeight="1">
-      <c r="A81" s="34"/>
-      <c r="B81" s="31"/>
-      <c r="C81" s="28"/>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="34"/>
-      <c r="B82" s="31"/>
-      <c r="C82" s="28"/>
-    </row>
-    <row r="83" spans="1:3" ht="32" customHeight="1">
-      <c r="A83" s="34"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="28"/>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="34"/>
-      <c r="B84" s="31"/>
-      <c r="C84" s="28"/>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="34"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="28"/>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="34"/>
-      <c r="B86" s="31"/>
-      <c r="C86" s="28"/>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="34"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="28"/>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="34"/>
-      <c r="B88" s="31"/>
-      <c r="C88" s="28"/>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="34"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="28"/>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="34"/>
-      <c r="B90" s="31"/>
-      <c r="C90" s="28"/>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="34"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="28"/>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="34"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="28"/>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="34"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="28"/>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="34"/>
-      <c r="B94" s="31"/>
-      <c r="C94" s="28"/>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="34"/>
-      <c r="B95" s="31"/>
-      <c r="C95" s="28"/>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="34"/>
-      <c r="B96" s="31"/>
-      <c r="C96" s="28"/>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="34"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="28"/>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="34"/>
-      <c r="B98" s="31"/>
-      <c r="C98" s="28"/>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="34"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="28"/>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="34"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="28"/>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="34"/>
-      <c r="B101" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C101" s="28"/>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="35"/>
-      <c r="B102" s="31"/>
-      <c r="C102" s="29"/>
-    </row>
-    <row r="103" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A103" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="B103" s="31"/>
-      <c r="C103" s="27" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="80" customHeight="1">
-      <c r="A104" s="34"/>
-      <c r="B104" s="31"/>
-      <c r="C104" s="28"/>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="34"/>
-      <c r="B105" s="31"/>
-      <c r="C105" s="28"/>
-    </row>
-    <row r="106" spans="1:3" ht="64" customHeight="1">
-      <c r="A106" s="34"/>
-      <c r="B106" s="31"/>
-      <c r="C106" s="28"/>
-    </row>
-    <row r="107" spans="1:3" ht="64" customHeight="1">
-      <c r="A107" s="34"/>
-      <c r="B107" s="31"/>
-      <c r="C107" s="28"/>
-    </row>
-    <row r="108" spans="1:3" ht="48" customHeight="1">
-      <c r="A108" s="34"/>
-      <c r="B108" s="31"/>
-      <c r="C108" s="28"/>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="34"/>
-      <c r="B109" s="31"/>
-      <c r="C109" s="28"/>
-    </row>
-    <row r="110" spans="1:3" ht="32" customHeight="1">
-      <c r="A110" s="34"/>
-      <c r="B110" s="31"/>
-      <c r="C110" s="28"/>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="34"/>
-      <c r="B111" s="31"/>
-      <c r="C111" s="28"/>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="34"/>
-      <c r="B112" s="31"/>
-      <c r="C112" s="28"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="34"/>
-      <c r="B113" s="31"/>
-      <c r="C113" s="28"/>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="34"/>
-      <c r="B114" s="31"/>
-      <c r="C114" s="28"/>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="34"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="28"/>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="34"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="28"/>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="34"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="28"/>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="34"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="28"/>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="34"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="28"/>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="34"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="28"/>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="34"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="28"/>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="34"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="28"/>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="34"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="28"/>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="34"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="28"/>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="34"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="28"/>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="34"/>
-      <c r="B126" s="32"/>
-      <c r="C126" s="28"/>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="34"/>
-      <c r="B127" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C127" s="28"/>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="35"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="29"/>
-    </row>
-    <row r="129" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A129" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="B129" s="31"/>
-      <c r="C129" s="27" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="80" customHeight="1">
-      <c r="A130" s="34"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="28"/>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="34"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="28"/>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="34"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="28"/>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="34"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="28"/>
-    </row>
-    <row r="134" spans="1:3" ht="48" customHeight="1">
-      <c r="A134" s="34"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="28"/>
-    </row>
-    <row r="135" spans="1:3" ht="80" customHeight="1">
-      <c r="A135" s="34"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="28"/>
-    </row>
-    <row r="136" spans="1:3" ht="64" customHeight="1">
-      <c r="A136" s="34"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="28"/>
-    </row>
-    <row r="137" spans="1:3" ht="32" customHeight="1">
-      <c r="A137" s="34"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="28"/>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="34"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="28"/>
-    </row>
-    <row r="139" spans="1:3" ht="80" customHeight="1">
-      <c r="A139" s="34"/>
-      <c r="B139" s="32"/>
-      <c r="C139" s="28"/>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" s="34"/>
-      <c r="B140" s="48">
-        <v>11012044</v>
-      </c>
-      <c r="C140" s="28"/>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" s="35"/>
-      <c r="B141" s="49"/>
-      <c r="C141" s="29"/>
-    </row>
-    <row r="142" spans="1:3" ht="404" customHeight="1">
-      <c r="A142" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="B142" s="49"/>
-      <c r="C142" s="27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="64" customHeight="1">
-      <c r="A143" s="34"/>
-      <c r="B143" s="49"/>
-      <c r="C143" s="28"/>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" s="34"/>
-      <c r="B144" s="49"/>
-      <c r="C144" s="28"/>
-    </row>
-    <row r="145" spans="1:3" ht="64" customHeight="1">
-      <c r="A145" s="34"/>
-      <c r="B145" s="49"/>
-      <c r="C145" s="28"/>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" s="34"/>
-      <c r="B146" s="49"/>
-      <c r="C146" s="28"/>
-    </row>
-    <row r="147" spans="1:3" ht="32" customHeight="1">
-      <c r="A147" s="34"/>
-      <c r="B147" s="49"/>
-      <c r="C147" s="28"/>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" s="34"/>
-      <c r="B148" s="49"/>
-      <c r="C148" s="28"/>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" s="34"/>
-      <c r="B149" s="49"/>
-      <c r="C149" s="28"/>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" s="34"/>
-      <c r="B150" s="49"/>
-      <c r="C150" s="28"/>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" s="34"/>
-      <c r="B151" s="49"/>
-      <c r="C151" s="28"/>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" s="34"/>
-      <c r="B152" s="49"/>
-      <c r="C152" s="28"/>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" s="34"/>
-      <c r="B153" s="49"/>
-      <c r="C153" s="28"/>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" s="34"/>
-      <c r="B154" s="49"/>
-      <c r="C154" s="28"/>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" s="34"/>
-      <c r="B155" s="50"/>
-      <c r="C155" s="28"/>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" s="34"/>
-      <c r="B156" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C156" s="28"/>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" s="35"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="29"/>
-    </row>
-    <row r="158" spans="1:3" ht="68" customHeight="1">
-      <c r="A158" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B158" s="32"/>
-      <c r="C158" s="27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="32" customHeight="1">
-      <c r="A159" s="34"/>
-      <c r="B159" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C159" s="28"/>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" s="35"/>
-      <c r="B160" s="32"/>
-      <c r="C160" s="29"/>
-    </row>
-    <row r="161" spans="1:3" ht="32" customHeight="1">
-      <c r="A161" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B161" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C161" s="25" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" s="57"/>
-      <c r="B162" s="31"/>
-      <c r="C162" s="26"/>
-    </row>
-    <row r="163" spans="1:3" ht="221" customHeight="1">
-      <c r="A163" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B163" s="31"/>
-      <c r="C163" s="27" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="48" customHeight="1">
-      <c r="A164" s="34"/>
-      <c r="B164" s="31"/>
-      <c r="C164" s="28"/>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="34"/>
-      <c r="B165" s="31"/>
-      <c r="C165" s="28"/>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="34"/>
-      <c r="B166" s="31"/>
-      <c r="C166" s="28"/>
-    </row>
-    <row r="167" spans="1:3" ht="32" customHeight="1">
-      <c r="A167" s="34"/>
-      <c r="B167" s="31"/>
-      <c r="C167" s="28"/>
-    </row>
-    <row r="168" spans="1:3" ht="32" customHeight="1">
-      <c r="A168" s="34"/>
-      <c r="B168" s="31"/>
-      <c r="C168" s="28"/>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="34"/>
-      <c r="B169" s="31"/>
-      <c r="C169" s="28"/>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="34"/>
-      <c r="B170" s="32"/>
-      <c r="C170" s="28"/>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" s="34"/>
-      <c r="B171" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C171" s="28"/>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" s="35"/>
-      <c r="B172" s="31"/>
-      <c r="C172" s="29"/>
-    </row>
-    <row r="173" spans="1:3" ht="238" customHeight="1">
-      <c r="A173" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="B173" s="31"/>
-      <c r="C173" s="27" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="32" customHeight="1">
-      <c r="A174" s="54"/>
-      <c r="B174" s="31"/>
-      <c r="C174" s="28"/>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" s="54"/>
-      <c r="B175" s="31"/>
-      <c r="C175" s="28"/>
-    </row>
-    <row r="176" spans="1:3" ht="32" customHeight="1">
-      <c r="A176" s="54"/>
-      <c r="B176" s="31"/>
-      <c r="C176" s="28"/>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="54"/>
-      <c r="B177" s="32"/>
-      <c r="C177" s="28"/>
-    </row>
-    <row r="178" spans="1:3" ht="64" customHeight="1">
-      <c r="A178" s="54"/>
-      <c r="B178" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C178" s="28"/>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" s="55"/>
-      <c r="B179" s="31"/>
-      <c r="C179" s="29"/>
-    </row>
-    <row r="180" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A180" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B180" s="31"/>
-      <c r="C180" s="27" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="48" customHeight="1">
-      <c r="A181" s="34"/>
-      <c r="B181" s="31"/>
-      <c r="C181" s="28"/>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="34"/>
-      <c r="B182" s="31"/>
-      <c r="C182" s="28"/>
-    </row>
-    <row r="183" spans="1:3" ht="64" customHeight="1">
-      <c r="A183" s="34"/>
-      <c r="B183" s="31"/>
-      <c r="C183" s="28"/>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" s="34"/>
-      <c r="B184" s="31"/>
-      <c r="C184" s="28"/>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" s="34"/>
-      <c r="B185" s="31"/>
-      <c r="C185" s="28"/>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" s="34"/>
-      <c r="B186" s="31"/>
-      <c r="C186" s="28"/>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" s="34"/>
-      <c r="B187" s="31"/>
-      <c r="C187" s="28"/>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" s="34"/>
-      <c r="B188" s="31"/>
-      <c r="C188" s="28"/>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" s="34"/>
-      <c r="B189" s="31"/>
-      <c r="C189" s="28"/>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" s="34"/>
-      <c r="B190" s="31"/>
-      <c r="C190" s="28"/>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" s="34"/>
-      <c r="B191" s="31"/>
-      <c r="C191" s="28"/>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="34"/>
-      <c r="B192" s="31"/>
-      <c r="C192" s="28"/>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" s="34"/>
-      <c r="B193" s="31"/>
-      <c r="C193" s="28"/>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" s="34"/>
-      <c r="B194" s="31"/>
-      <c r="C194" s="28"/>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" s="34"/>
-      <c r="B195" s="31"/>
-      <c r="C195" s="28"/>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196" s="34"/>
-      <c r="B196" s="31"/>
-      <c r="C196" s="28"/>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197" s="34"/>
-      <c r="B197" s="31"/>
-      <c r="C197" s="28"/>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" s="34"/>
-      <c r="B198" s="31"/>
-      <c r="C198" s="28"/>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" s="34"/>
-      <c r="B199" s="32"/>
-      <c r="C199" s="28"/>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" s="34"/>
-      <c r="B200" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C200" s="28"/>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" s="35"/>
-      <c r="B201" s="32"/>
-      <c r="C201" s="29"/>
-    </row>
-    <row r="202" spans="1:3" ht="48" customHeight="1">
-      <c r="A202" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B202" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C202" s="25" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" s="35"/>
-      <c r="B203" s="31"/>
-      <c r="C203" s="26"/>
-    </row>
-    <row r="204" spans="1:3" ht="255" customHeight="1">
-      <c r="A204" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B204" s="31"/>
-      <c r="C204" s="27" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="96" customHeight="1">
-      <c r="A205" s="34"/>
-      <c r="B205" s="31"/>
-      <c r="C205" s="28"/>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" s="34"/>
-      <c r="B206" s="31"/>
-      <c r="C206" s="28"/>
-    </row>
-    <row r="207" spans="1:3" ht="32" customHeight="1">
-      <c r="A207" s="34"/>
-      <c r="B207" s="31"/>
-      <c r="C207" s="28"/>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" s="34"/>
-      <c r="B208" s="31"/>
-      <c r="C208" s="28"/>
-    </row>
-    <row r="209" spans="1:3">
-      <c r="A209" s="34"/>
-      <c r="B209" s="32"/>
-      <c r="C209" s="28"/>
-    </row>
-    <row r="210" spans="1:3">
-      <c r="A210" s="34"/>
-      <c r="B210" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C210" s="28"/>
-    </row>
-    <row r="211" spans="1:3">
-      <c r="A211" s="35"/>
-      <c r="B211" s="31"/>
-      <c r="C211" s="29"/>
-    </row>
-    <row r="212" spans="1:3" ht="255" customHeight="1">
-      <c r="A212" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="B212" s="31"/>
-      <c r="C212" s="27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3">
-      <c r="A213" s="34"/>
-      <c r="B213" s="31"/>
-      <c r="C213" s="28"/>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="34"/>
-      <c r="B214" s="31"/>
-      <c r="C214" s="28"/>
-    </row>
-    <row r="215" spans="1:3">
-      <c r="A215" s="34"/>
-      <c r="B215" s="31"/>
-      <c r="C215" s="28"/>
-    </row>
-    <row r="216" spans="1:3">
-      <c r="A216" s="34"/>
-      <c r="B216" s="31"/>
-      <c r="C216" s="28"/>
-    </row>
-    <row r="217" spans="1:3">
-      <c r="A217" s="34"/>
-      <c r="B217" s="31"/>
-      <c r="C217" s="28"/>
-    </row>
-    <row r="218" spans="1:3">
-      <c r="A218" s="34"/>
-      <c r="B218" s="31"/>
-      <c r="C218" s="28"/>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="34"/>
-      <c r="B219" s="31"/>
-      <c r="C219" s="28"/>
-    </row>
-    <row r="220" spans="1:3">
-      <c r="A220" s="34"/>
-      <c r="B220" s="31"/>
-      <c r="C220" s="28"/>
-    </row>
-    <row r="221" spans="1:3">
-      <c r="A221" s="34"/>
-      <c r="B221" s="32"/>
-      <c r="C221" s="28"/>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="A222" s="34"/>
-      <c r="B222" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C222" s="28"/>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" s="35"/>
-      <c r="B223" s="31"/>
-      <c r="C223" s="29"/>
-    </row>
-    <row r="224" spans="1:3" ht="102" customHeight="1">
-      <c r="A224" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B224" s="31"/>
-      <c r="C224" s="27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="48" customHeight="1">
-      <c r="A225" s="34"/>
-      <c r="B225" s="32"/>
-      <c r="C225" s="28"/>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="34"/>
-      <c r="B226" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C226" s="28"/>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="35"/>
-      <c r="B227" s="31"/>
-      <c r="C227" s="29"/>
-    </row>
-    <row r="228" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A228" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B228" s="31"/>
-      <c r="C228" s="27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="32" customHeight="1">
-      <c r="A229" s="34"/>
-      <c r="B229" s="31"/>
-      <c r="C229" s="28"/>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="34"/>
-      <c r="B230" s="31"/>
-      <c r="C230" s="28"/>
-    </row>
-    <row r="231" spans="1:3" ht="48" customHeight="1">
-      <c r="A231" s="34"/>
-      <c r="B231" s="31"/>
-      <c r="C231" s="28"/>
-    </row>
-    <row r="232" spans="1:3" ht="48" customHeight="1">
-      <c r="A232" s="34"/>
-      <c r="B232" s="31"/>
-      <c r="C232" s="28"/>
-    </row>
-    <row r="233" spans="1:3" ht="64" customHeight="1">
-      <c r="A233" s="34"/>
-      <c r="B233" s="31"/>
-      <c r="C233" s="28"/>
-    </row>
-    <row r="234" spans="1:3" ht="48" customHeight="1">
-      <c r="A234" s="34"/>
-      <c r="B234" s="31"/>
-      <c r="C234" s="28"/>
-    </row>
-    <row r="235" spans="1:3" ht="48" customHeight="1">
-      <c r="A235" s="34"/>
-      <c r="B235" s="31"/>
-      <c r="C235" s="28"/>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="34"/>
-      <c r="B236" s="31"/>
-      <c r="C236" s="28"/>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237" s="34"/>
-      <c r="B237" s="31"/>
-      <c r="C237" s="28"/>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238" s="34"/>
-      <c r="B238" s="31"/>
-      <c r="C238" s="28"/>
-    </row>
-    <row r="239" spans="1:3" ht="32" customHeight="1">
-      <c r="A239" s="34"/>
-      <c r="B239" s="31"/>
-      <c r="C239" s="28"/>
-    </row>
-    <row r="240" spans="1:3" ht="32" customHeight="1">
-      <c r="A240" s="34"/>
-      <c r="B240" s="31"/>
-      <c r="C240" s="28"/>
-    </row>
-    <row r="241" spans="1:3" ht="32" customHeight="1">
-      <c r="A241" s="34"/>
-      <c r="B241" s="31"/>
-      <c r="C241" s="28"/>
-    </row>
-    <row r="242" spans="1:3" ht="32" customHeight="1">
-      <c r="A242" s="34"/>
-      <c r="B242" s="32"/>
-      <c r="C242" s="28"/>
-    </row>
-    <row r="243" spans="1:3" ht="32" customHeight="1">
-      <c r="A243" s="34"/>
-      <c r="B243" s="40">
-        <v>15472</v>
-      </c>
-      <c r="C243" s="28"/>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244" s="35"/>
-      <c r="B244" s="41"/>
-      <c r="C244" s="29"/>
-    </row>
-    <row r="245" spans="1:3" ht="289" customHeight="1">
-      <c r="A245" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="B245" s="41"/>
-      <c r="C245" s="27" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="80" customHeight="1">
-      <c r="A246" s="44"/>
-      <c r="B246" s="41"/>
-      <c r="C246" s="28"/>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" s="44"/>
-      <c r="B247" s="41"/>
-      <c r="C247" s="28"/>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248" s="44"/>
-      <c r="B248" s="41"/>
-      <c r="C248" s="28"/>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" s="44"/>
-      <c r="B249" s="41"/>
-      <c r="C249" s="28"/>
-    </row>
-    <row r="250" spans="1:3" ht="32" customHeight="1">
-      <c r="A250" s="44"/>
-      <c r="B250" s="41"/>
-      <c r="C250" s="28"/>
-    </row>
-    <row r="251" spans="1:3" ht="32" customHeight="1">
-      <c r="A251" s="44"/>
-      <c r="B251" s="41"/>
-      <c r="C251" s="28"/>
-    </row>
-    <row r="252" spans="1:3" ht="32" customHeight="1">
-      <c r="A252" s="44"/>
-      <c r="B252" s="42"/>
-      <c r="C252" s="28"/>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253" s="44"/>
-      <c r="B253" s="46">
-        <v>75009240</v>
-      </c>
-      <c r="C253" s="28"/>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254" s="45"/>
-      <c r="B254" s="47"/>
-      <c r="C254" s="29"/>
-    </row>
-    <row r="255" spans="1:3">
-      <c r="A255" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="B255" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="C255" s="25" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256" s="52"/>
-      <c r="B256" s="31"/>
-      <c r="C256" s="26"/>
-    </row>
-    <row r="257" spans="1:3" ht="388" customHeight="1">
-      <c r="A257" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="B257" s="31"/>
-      <c r="C257" s="27" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258" s="34"/>
-      <c r="B258" s="31"/>
-      <c r="C258" s="28"/>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" s="34"/>
-      <c r="B259" s="31"/>
-      <c r="C259" s="28"/>
-    </row>
-    <row r="260" spans="1:3" ht="48" customHeight="1">
-      <c r="A260" s="34"/>
-      <c r="B260" s="31"/>
-      <c r="C260" s="28"/>
-    </row>
-    <row r="261" spans="1:3" ht="32" customHeight="1">
-      <c r="A261" s="34"/>
-      <c r="B261" s="31"/>
-      <c r="C261" s="28"/>
-    </row>
-    <row r="262" spans="1:3" ht="32" customHeight="1">
-      <c r="A262" s="34"/>
-      <c r="B262" s="31"/>
-      <c r="C262" s="28"/>
-    </row>
-    <row r="263" spans="1:3" ht="32" customHeight="1">
-      <c r="A263" s="34"/>
-      <c r="B263" s="31"/>
-      <c r="C263" s="28"/>
-    </row>
-    <row r="264" spans="1:3">
-      <c r="A264" s="34"/>
-      <c r="B264" s="31"/>
-      <c r="C264" s="28"/>
-    </row>
-    <row r="265" spans="1:3">
-      <c r="A265" s="34"/>
-      <c r="B265" s="31"/>
-      <c r="C265" s="28"/>
-    </row>
-    <row r="266" spans="1:3">
-      <c r="A266" s="34"/>
-      <c r="B266" s="31"/>
-      <c r="C266" s="28"/>
-    </row>
-    <row r="267" spans="1:3">
-      <c r="A267" s="34"/>
-      <c r="B267" s="31"/>
-      <c r="C267" s="28"/>
-    </row>
-    <row r="268" spans="1:3">
-      <c r="A268" s="34"/>
-      <c r="B268" s="31"/>
-      <c r="C268" s="28"/>
-    </row>
-    <row r="269" spans="1:3">
-      <c r="A269" s="34"/>
-      <c r="B269" s="31"/>
-      <c r="C269" s="28"/>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270" s="34"/>
-      <c r="B270" s="32"/>
-      <c r="C270" s="28"/>
-    </row>
-    <row r="271" spans="1:3">
-      <c r="A271" s="34"/>
-      <c r="B271" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C271" s="28"/>
-    </row>
-    <row r="272" spans="1:3">
-      <c r="A272" s="35"/>
-      <c r="B272" s="31"/>
-      <c r="C272" s="29"/>
-    </row>
-    <row r="273" spans="1:3" ht="306" customHeight="1">
-      <c r="A273" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="B273" s="31"/>
-      <c r="C273" s="27" t="s">
-        <v>232</v>
-      </c>
-    </row>
     <row r="274" spans="1:3">
-      <c r="A274" s="31"/>
-      <c r="B274" s="31"/>
-      <c r="C274" s="28"/>
+      <c r="A274" s="38"/>
+      <c r="B274" s="38"/>
+      <c r="C274" s="63"/>
     </row>
     <row r="275" spans="1:3" ht="48" customHeight="1">
-      <c r="A275" s="31"/>
-      <c r="B275" s="31"/>
-      <c r="C275" s="28"/>
+      <c r="A275" s="38"/>
+      <c r="B275" s="38"/>
+      <c r="C275" s="63"/>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="31"/>
-      <c r="B276" s="31"/>
-      <c r="C276" s="28"/>
+      <c r="A276" s="38"/>
+      <c r="B276" s="38"/>
+      <c r="C276" s="63"/>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="31"/>
-      <c r="B277" s="31"/>
-      <c r="C277" s="28"/>
+      <c r="A277" s="38"/>
+      <c r="B277" s="38"/>
+      <c r="C277" s="63"/>
     </row>
     <row r="278" spans="1:3">
-      <c r="A278" s="31"/>
-      <c r="B278" s="31"/>
-      <c r="C278" s="28"/>
+      <c r="A278" s="38"/>
+      <c r="B278" s="38"/>
+      <c r="C278" s="63"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="31"/>
-      <c r="B279" s="31"/>
-      <c r="C279" s="28"/>
+      <c r="A279" s="38"/>
+      <c r="B279" s="38"/>
+      <c r="C279" s="63"/>
     </row>
     <row r="280" spans="1:3" ht="32" customHeight="1">
-      <c r="A280" s="31"/>
-      <c r="B280" s="31"/>
-      <c r="C280" s="28"/>
+      <c r="A280" s="38"/>
+      <c r="B280" s="38"/>
+      <c r="C280" s="63"/>
     </row>
     <row r="281" spans="1:3">
-      <c r="A281" s="31"/>
-      <c r="B281" s="31"/>
-      <c r="C281" s="28"/>
+      <c r="A281" s="38"/>
+      <c r="B281" s="38"/>
+      <c r="C281" s="63"/>
     </row>
     <row r="282" spans="1:3">
-      <c r="A282" s="31"/>
-      <c r="B282" s="31"/>
-      <c r="C282" s="28"/>
+      <c r="A282" s="38"/>
+      <c r="B282" s="38"/>
+      <c r="C282" s="63"/>
     </row>
     <row r="283" spans="1:3">
-      <c r="A283" s="31"/>
-      <c r="B283" s="31"/>
-      <c r="C283" s="28"/>
+      <c r="A283" s="38"/>
+      <c r="B283" s="38"/>
+      <c r="C283" s="63"/>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="31"/>
-      <c r="B284" s="31"/>
-      <c r="C284" s="28"/>
+      <c r="A284" s="38"/>
+      <c r="B284" s="38"/>
+      <c r="C284" s="63"/>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="31"/>
-      <c r="B285" s="32"/>
-      <c r="C285" s="28"/>
+      <c r="A285" s="38"/>
+      <c r="B285" s="35"/>
+      <c r="C285" s="63"/>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286" s="31"/>
-      <c r="C286" s="28"/>
+      <c r="A286" s="38"/>
+      <c r="C286" s="63"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="31"/>
-      <c r="C287" s="29"/>
+      <c r="A287" s="38"/>
+      <c r="C287" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="77">
+    <mergeCell ref="C255:C256"/>
+    <mergeCell ref="C257:C272"/>
+    <mergeCell ref="C273:C287"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="C204:C211"/>
+    <mergeCell ref="C212:C223"/>
+    <mergeCell ref="C224:C227"/>
+    <mergeCell ref="C228:C244"/>
+    <mergeCell ref="C245:C254"/>
+    <mergeCell ref="C180:C201"/>
+    <mergeCell ref="C13:C19"/>
+    <mergeCell ref="C35:C45"/>
+    <mergeCell ref="C20:C34"/>
+    <mergeCell ref="C46:C73"/>
+    <mergeCell ref="C74:C102"/>
+    <mergeCell ref="C103:C128"/>
+    <mergeCell ref="C129:C141"/>
+    <mergeCell ref="C142:C157"/>
+    <mergeCell ref="C158:C160"/>
+    <mergeCell ref="C161:C162"/>
+    <mergeCell ref="C163:C172"/>
+    <mergeCell ref="C173:C179"/>
+    <mergeCell ref="B255:B270"/>
+    <mergeCell ref="A257:A272"/>
+    <mergeCell ref="B271:B285"/>
+    <mergeCell ref="A273:A287"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="B202:B209"/>
+    <mergeCell ref="A204:A211"/>
+    <mergeCell ref="B210:B221"/>
+    <mergeCell ref="A212:A223"/>
+    <mergeCell ref="B222:B225"/>
+    <mergeCell ref="A224:A227"/>
+    <mergeCell ref="B156:B158"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="B44:B71"/>
+    <mergeCell ref="A46:A73"/>
+    <mergeCell ref="B72:B100"/>
+    <mergeCell ref="A74:A102"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B243:B252"/>
+    <mergeCell ref="A245:A254"/>
+    <mergeCell ref="B253:B254"/>
+    <mergeCell ref="B171:B177"/>
+    <mergeCell ref="B127:B139"/>
+    <mergeCell ref="A129:A141"/>
+    <mergeCell ref="B140:B155"/>
+    <mergeCell ref="A142:A157"/>
+    <mergeCell ref="B101:B126"/>
+    <mergeCell ref="A103:A128"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B18:B32"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B10"/>
@@ -7253,67 +8045,6 @@
     <mergeCell ref="A161:A162"/>
     <mergeCell ref="B161:B170"/>
     <mergeCell ref="A163:A172"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B243:B252"/>
-    <mergeCell ref="A245:A254"/>
-    <mergeCell ref="B253:B254"/>
-    <mergeCell ref="B171:B177"/>
-    <mergeCell ref="B127:B139"/>
-    <mergeCell ref="A129:A141"/>
-    <mergeCell ref="B140:B155"/>
-    <mergeCell ref="A142:A157"/>
-    <mergeCell ref="B101:B126"/>
-    <mergeCell ref="A103:A128"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="B18:B32"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A35:A45"/>
-    <mergeCell ref="B44:B71"/>
-    <mergeCell ref="A46:A73"/>
-    <mergeCell ref="B72:B100"/>
-    <mergeCell ref="A74:A102"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B255:B270"/>
-    <mergeCell ref="A257:A272"/>
-    <mergeCell ref="B271:B285"/>
-    <mergeCell ref="A273:A287"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="B202:B209"/>
-    <mergeCell ref="A204:A211"/>
-    <mergeCell ref="B210:B221"/>
-    <mergeCell ref="A212:A223"/>
-    <mergeCell ref="B222:B225"/>
-    <mergeCell ref="A224:A227"/>
-    <mergeCell ref="B156:B158"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="C180:C201"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="C35:C45"/>
-    <mergeCell ref="C20:C34"/>
-    <mergeCell ref="C46:C73"/>
-    <mergeCell ref="C74:C102"/>
-    <mergeCell ref="C103:C128"/>
-    <mergeCell ref="C129:C141"/>
-    <mergeCell ref="C142:C157"/>
-    <mergeCell ref="C158:C160"/>
-    <mergeCell ref="C161:C162"/>
-    <mergeCell ref="C163:C172"/>
-    <mergeCell ref="C173:C179"/>
-    <mergeCell ref="C255:C256"/>
-    <mergeCell ref="C257:C272"/>
-    <mergeCell ref="C273:C287"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="C204:C211"/>
-    <mergeCell ref="C212:C223"/>
-    <mergeCell ref="C224:C227"/>
-    <mergeCell ref="C228:C244"/>
-    <mergeCell ref="C245:C254"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7322,513 +8053,766 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D8B340-9ADC-414D-AE14-655ED59327F9}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" thickBot="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="409.6" thickBot="1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="34">
+      <c r="A2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="68">
+      <c r="A3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="68">
+      <c r="A4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="102">
+      <c r="A5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="34">
+      <c r="A6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17">
+      <c r="A7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="51">
+      <c r="A8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="409.6">
+      <c r="A9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="85">
+      <c r="A10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="68">
+      <c r="A11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="51">
+      <c r="A12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="68">
+      <c r="A13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17">
+      <c r="A14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="51">
+      <c r="A15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="102">
+      <c r="A16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="85">
+      <c r="A17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="68">
+      <c r="A18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="34">
+      <c r="A19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17">
+      <c r="A20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="68">
+      <c r="A21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="102">
+      <c r="A22" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="409.6">
+      <c r="A23" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B23" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" t="s">
+    <row r="24" spans="1:3" ht="17">
+      <c r="A24" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C24" s="67" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="409.6" thickBot="1">
-      <c r="A4" s="15" t="s">
+    <row r="25" spans="1:3" ht="409.6">
+      <c r="A25" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B25" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C25" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="69" thickBot="1">
-      <c r="A5" s="4" t="s">
+    <row r="26" spans="1:3" ht="68">
+      <c r="A26" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B26" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C26" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="35" thickBot="1">
-      <c r="A6" s="4" t="s">
+    <row r="27" spans="1:3" ht="34">
+      <c r="A27" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B27" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C27" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="52" thickBot="1">
-      <c r="A7" s="2" t="s">
+    <row r="28" spans="1:3" ht="51">
+      <c r="A28" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B28" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C28" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="35" thickBot="1">
-      <c r="A8" s="2" t="s">
+    <row r="29" spans="1:3" ht="34">
+      <c r="A29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B29" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="52" thickBot="1">
-      <c r="A9" s="4" t="s">
+    <row r="30" spans="1:3" ht="51">
+      <c r="A30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B30" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="35" thickBot="1">
-      <c r="A10" s="2" t="s">
+    <row r="31" spans="1:3" ht="34">
+      <c r="A31" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B31" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C31" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="52" thickBot="1">
-      <c r="A11" s="2" t="s">
+    <row r="32" spans="1:3" ht="51">
+      <c r="A32" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B32" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C32" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="52" thickBot="1">
-      <c r="A12" s="2" t="s">
+    <row r="33" spans="1:3" ht="51">
+      <c r="A33" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B33" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C33" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="86" thickBot="1">
-      <c r="A13" s="2" t="s">
+    <row r="34" spans="1:3" ht="85">
+      <c r="A34" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B34" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C34" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="35" thickBot="1">
-      <c r="A14" s="2" t="s">
+    <row r="35" spans="1:3" ht="34">
+      <c r="A35" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="52" thickBot="1">
-      <c r="A15" s="4" t="s">
+    <row r="36" spans="1:3" ht="187">
+      <c r="A36" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="51">
+      <c r="A37" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B37" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="52" thickBot="1">
-      <c r="A16" s="4" t="s">
+    <row r="38" spans="1:3" ht="51">
+      <c r="A38" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B38" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C38" s="10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="86" thickBot="1">
-      <c r="A17" s="4" t="s">
+    <row r="39" spans="1:3" ht="85">
+      <c r="A39" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B39" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C39" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="154" thickBot="1">
-      <c r="A18" s="4" t="s">
+    <row r="40" spans="1:3" ht="153">
+      <c r="A40" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B40" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C40" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="86" thickBot="1">
-      <c r="A19" s="3" t="s">
+    <row r="41" spans="1:3" ht="85">
+      <c r="A41" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B41" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C41" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="239" thickBot="1">
-      <c r="A20" s="2" t="s">
+    <row r="42" spans="1:3" ht="238">
+      <c r="A42" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B42" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C42" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="137" thickBot="1">
-      <c r="A21" s="2" t="s">
+    <row r="43" spans="1:3" ht="136">
+      <c r="A43" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B43" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C43" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="86" thickBot="1">
-      <c r="A22" s="4" t="s">
+    <row r="44" spans="1:3" ht="85">
+      <c r="A44" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B44" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C44" s="10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="171" thickBot="1">
-      <c r="A23" s="2" t="s">
+    <row r="45" spans="1:3" ht="136">
+      <c r="A45" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B45" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C45" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="137" thickBot="1">
-      <c r="A24" s="2" t="s">
+    <row r="46" spans="1:3" ht="85">
+      <c r="A46" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B46" s="11">
+        <v>4469605</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="47" spans="1:3" ht="238">
+      <c r="A47" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="86" thickBot="1">
-      <c r="A25" s="2" t="s">
+      <c r="B47" s="11">
+        <v>75009240</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="2">
-        <v>4469605</v>
-      </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="48" spans="1:3" ht="136">
+      <c r="A48" s="11" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="239" thickBot="1">
-      <c r="A26" s="2" t="s">
+      <c r="B48" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="2">
-        <v>75009240</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="C48" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="137" thickBot="1">
-      <c r="A27" s="2" t="s">
+    <row r="49" spans="1:3" ht="136">
+      <c r="A49" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B49" s="11">
+        <v>12579017</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="50" spans="1:3" ht="102">
+      <c r="A50" s="11" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="18" thickBot="1">
-      <c r="A28" s="4" t="s">
+      <c r="B50" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="17">
+      <c r="A51" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="11">
+        <v>34577</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="388">
+      <c r="A52" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B28" s="4">
-        <v>34577</v>
-      </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="53" spans="1:3" ht="68">
+      <c r="A53" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="103" thickBot="1">
-      <c r="A29" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="389" thickBot="1">
-      <c r="A30" s="4" t="s">
+      <c r="B53" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="54" spans="1:3" ht="102">
+      <c r="A54" s="11" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="69" thickBot="1">
-      <c r="A31" s="4" t="s">
+      <c r="B54" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="C54" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="103" thickBot="1">
-      <c r="A32" s="4" t="s">
+    <row r="55" spans="1:3" ht="51">
+      <c r="A55" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B55" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="56" spans="1:3" ht="85">
+      <c r="A56" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="153">
+      <c r="A57" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="52" thickBot="1">
-      <c r="A33" s="4" t="s">
+      <c r="B57" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="C57" s="10" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="154" thickBot="1">
-      <c r="A34" s="4" t="s">
+    <row r="58" spans="1:3" ht="68">
+      <c r="A58" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B58" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C58" s="10" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="69" thickBot="1">
-      <c r="A35" s="4" t="s">
+    <row r="59" spans="1:3" ht="85">
+      <c r="A59" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B59" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="60" spans="1:3" ht="153">
+      <c r="A60" s="11" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="86" thickBot="1">
-      <c r="A36" s="4" t="s">
+      <c r="B60" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="C60" s="10" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="154" thickBot="1">
-      <c r="A37" s="4" t="s">
+    <row r="61" spans="1:3" ht="102">
+      <c r="A61" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B61" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="62" spans="1:3" ht="85">
+      <c r="A62" s="11" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="103" thickBot="1">
-      <c r="A38" s="4" t="s">
+      <c r="B62" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="C62" s="10" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="86" thickBot="1">
-      <c r="A39" s="4" t="s">
+    <row r="63" spans="1:3" ht="119">
+      <c r="A63" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B63" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C63" s="10" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="120" thickBot="1">
-      <c r="A40" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C40" t="s">
+    <row r="64" spans="1:3" ht="34">
+      <c r="A64" s="12" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="86" thickBot="1">
-      <c r="A41" s="4" t="s">
+      <c r="B64" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="65" spans="1:3" ht="102">
+      <c r="A65" s="12" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="35" thickBot="1">
-      <c r="A42" s="3" t="s">
+      <c r="B65" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="66" spans="1:3" ht="85">
+      <c r="A66" s="69" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="103" thickBot="1">
-      <c r="A43" s="8" t="s">
+      <c r="B66" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="67" spans="1:3" ht="85">
+      <c r="A67" s="11" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="86" thickBot="1">
-      <c r="A44" s="9" t="s">
+      <c r="B67" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="68" spans="1:3" ht="102">
+      <c r="A68" s="11" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="86" thickBot="1">
-      <c r="A45" s="4" t="s">
+      <c r="B68" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C45" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="102">
-      <c r="A46" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" t="s">
-        <v>163</v>
+    </row>
+    <row r="69" spans="1:3" ht="187">
+      <c r="A69" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -7838,7 +8822,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D3CFEF-7051-E441-912E-91AFA4B7E1A1}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17" thickBot="1">
@@ -7853,68 +8837,750 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="35" thickBot="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="69" thickBot="1">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="69" thickBot="1">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="103" thickBot="1">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="35" thickBot="1">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="52" thickBot="1">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="409.6" thickBot="1">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="86" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="69" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="52" thickBot="1">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="69" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" thickBot="1">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="52" thickBot="1">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="103" thickBot="1">
+      <c r="A16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="86" thickBot="1">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="69" thickBot="1">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="35" thickBot="1">
+      <c r="A19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" thickBot="1">
+      <c r="A20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="69" thickBot="1">
+      <c r="A21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="103" thickBot="1">
+      <c r="A22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="409.6" thickBot="1">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18" thickBot="1">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="409.6" thickBot="1">
+      <c r="A25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="69" thickBot="1">
+      <c r="A26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="35" thickBot="1">
+      <c r="A27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="52" thickBot="1">
+      <c r="A28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="35" thickBot="1">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="52" thickBot="1">
+      <c r="A30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="35" thickBot="1">
+      <c r="A31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="52" thickBot="1">
+      <c r="A32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="52" thickBot="1">
+      <c r="A33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="86" thickBot="1">
+      <c r="A34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="35" thickBot="1">
+      <c r="A35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="188" thickBot="1">
+      <c r="A36" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="52" thickBot="1">
+      <c r="A37" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="52" thickBot="1">
+      <c r="A38" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="86" thickBot="1">
+      <c r="A39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="154" thickBot="1">
+      <c r="A40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="86" thickBot="1">
+      <c r="A41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="239" thickBot="1">
+      <c r="A42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="137" thickBot="1">
+      <c r="A43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="86" thickBot="1">
+      <c r="A44" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="137" thickBot="1">
+      <c r="A45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="86" thickBot="1">
+      <c r="A46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="2">
+        <v>4469605</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="239" thickBot="1">
+      <c r="A47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="2">
+        <v>75009240</v>
+      </c>
+      <c r="C47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="137" thickBot="1">
+      <c r="A48" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="137" thickBot="1">
+      <c r="A49" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="4">
+        <v>12579017</v>
+      </c>
+      <c r="C49" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="103" thickBot="1">
+      <c r="A50" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18" thickBot="1">
+      <c r="A51" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="4">
+        <v>34577</v>
+      </c>
+      <c r="C51" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="389" thickBot="1">
+      <c r="A52" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="69" thickBot="1">
+      <c r="A53" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="103" thickBot="1">
+      <c r="A54" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="52" thickBot="1">
+      <c r="A55" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="86" thickBot="1">
+      <c r="A56" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="154" thickBot="1">
+      <c r="A57" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="69" thickBot="1">
+      <c r="A58" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="86" thickBot="1">
+      <c r="A59" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="154" thickBot="1">
+      <c r="A60" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="103" thickBot="1">
+      <c r="A61" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C61" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="86" thickBot="1">
+      <c r="A62" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="120" thickBot="1">
+      <c r="A63" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="35" thickBot="1">
+      <c r="A64" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="103" thickBot="1">
+      <c r="A65" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="66" spans="1:3" ht="86" thickBot="1">
+      <c r="A66" s="9" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="103" thickBot="1">
-      <c r="A3" s="8" t="s">
+      <c r="B66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="67" spans="1:3" ht="86" thickBot="1">
+      <c r="A67" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="86" thickBot="1">
-      <c r="A4" s="9" t="s">
+      <c r="B67" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="68" spans="1:3" ht="102">
+      <c r="A68" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="86" thickBot="1">
-      <c r="A5" s="4" t="s">
+      <c r="B68" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="102">
-      <c r="A6" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="187">
-      <c r="A7" s="11" t="s">
+    </row>
+    <row r="69" spans="1:3" ht="187">
+      <c r="A69" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B69" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C69" s="10" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7929,278 +9595,278 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:3" ht="32">
-      <c r="A1" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>265</v>
+      <c r="A1" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="170">
-      <c r="A2" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>267</v>
+      <c r="C2" s="22" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="409.6">
-      <c r="A3" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="409.6">
-      <c r="A4" s="18" t="s">
+      <c r="C3" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="221">
+      <c r="A4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="221">
-      <c r="A5" s="18" t="s">
+      <c r="C4" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="255">
+      <c r="A5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="255">
-      <c r="A6" s="18" t="s">
+      <c r="C5" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="187">
+      <c r="A6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="153">
-      <c r="A7" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="C6" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="409.6">
+      <c r="A7" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>33</v>
+      <c r="C7" s="5" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="409.6">
-      <c r="A8" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="19" t="s">
+      <c r="A8" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>273</v>
+      <c r="C8" s="5" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="409.6">
-      <c r="A9" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>274</v>
+      <c r="C9" s="5" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="409.6">
-      <c r="A10" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>275</v>
+      <c r="C10" s="5" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="409.6">
-      <c r="A11" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="19" t="s">
+      <c r="A11" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>276</v>
+      <c r="C11" s="5" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="409.6">
-      <c r="A12" s="18" t="s">
-        <v>207</v>
+      <c r="A12" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>277</v>
+      <c r="C12" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="409.6">
-      <c r="A13" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="A13" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="19">
         <v>11012044</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>278</v>
+      <c r="C13" s="5" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="409.6">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>279</v>
+      <c r="B14" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="409.6">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>280</v>
+      <c r="B15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="409.6">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>281</v>
+      <c r="B16" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="409.6">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>282</v>
+      <c r="B17" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="409.6">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="409.6">
-      <c r="A19" s="18" t="s">
+      <c r="B18" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="323">
+      <c r="A19" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>284</v>
+      <c r="B19" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="409.6">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>285</v>
+      <c r="B20" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="409.6">
-      <c r="A21" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="238">
-      <c r="A22" s="18" t="s">
+      <c r="A21" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="409.6">
+      <c r="A22" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>287</v>
+      <c r="B22" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="409.6">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>87</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>288</v>
+      <c r="C23" s="5" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="409.6">
-      <c r="A24" s="18" t="s">
-        <v>136</v>
+      <c r="A24" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>289</v>
+        <v>232</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="409.6">
-      <c r="A25" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>290</v>
+      <c r="A25" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -8214,278 +9880,278 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:3" ht="32">
-      <c r="A1" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>265</v>
+      <c r="A1" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="170">
-      <c r="A2" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>267</v>
+      <c r="C2" s="22" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="409.6">
-      <c r="A3" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="409.6">
-      <c r="A4" s="18" t="s">
+      <c r="C3" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="221">
+      <c r="A4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="221">
-      <c r="A5" s="18" t="s">
+      <c r="C4" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="255">
+      <c r="A5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="255">
-      <c r="A6" s="18" t="s">
+      <c r="C5" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="187">
+      <c r="A6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="153">
-      <c r="A7" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="C6" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="409.6">
+      <c r="A7" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>33</v>
+      <c r="C7" s="5" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="409.6">
-      <c r="A8" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="19" t="s">
+      <c r="A8" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>273</v>
+      <c r="C8" s="5" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="409.6">
-      <c r="A9" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>274</v>
+      <c r="C9" s="5" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="409.6">
-      <c r="A10" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>275</v>
+      <c r="C10" s="5" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="409.6">
-      <c r="A11" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="19" t="s">
+      <c r="A11" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>276</v>
+      <c r="C11" s="5" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="409.6">
-      <c r="A12" s="18" t="s">
-        <v>207</v>
+      <c r="A12" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>277</v>
+      <c r="C12" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="409.6">
-      <c r="A13" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="A13" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="19">
         <v>11012044</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>278</v>
+      <c r="C13" s="5" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="409.6">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>279</v>
+      <c r="B14" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="409.6">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>280</v>
+      <c r="B15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="409.6">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>281</v>
+      <c r="B16" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="409.6">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>282</v>
+      <c r="B17" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="409.6">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="409.6">
-      <c r="A19" s="18" t="s">
+      <c r="B18" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="323">
+      <c r="A19" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>284</v>
+      <c r="B19" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="409.6">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>285</v>
+      <c r="B20" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="409.6">
-      <c r="A21" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="238">
-      <c r="A22" s="18" t="s">
+      <c r="A21" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="409.6">
+      <c r="A22" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>287</v>
+      <c r="B22" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="409.6">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>87</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>288</v>
+      <c r="C23" s="5" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="409.6">
-      <c r="A24" s="18" t="s">
-        <v>136</v>
+      <c r="A24" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>289</v>
+        <v>232</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="409.6">
-      <c r="A25" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>290</v>
+      <c r="A25" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -8495,453 +10161,85 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B4AA823-ECC9-2447-9229-13F44AAC3649}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="79.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="409.6">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="5" t="s">
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="13" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="409.6">
-      <c r="A3" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="409.6">
-      <c r="A4" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="5" t="s">
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="13" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="409.6">
-      <c r="A5" s="13" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="5" t="s">
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="13" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="372">
-      <c r="A6" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18">
-      <c r="A7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="238">
-      <c r="A9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="409.6">
-      <c r="A10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="409.6">
-      <c r="A11" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="409.6">
-      <c r="A12" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="51">
-      <c r="A14" s="12" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="68">
-      <c r="A15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="17">
-      <c r="A16" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="51">
-      <c r="A17" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="102">
-      <c r="A18" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="85">
-      <c r="A19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="68">
-      <c r="A20" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="34">
-      <c r="A21" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="17">
-      <c r="A22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="68">
-      <c r="A23" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="103" thickBot="1">
-      <c r="A24" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="409.6" thickBot="1">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="18" thickBot="1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="409.6">
-      <c r="A27" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="68">
-      <c r="A28" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="34">
-      <c r="A29" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="51">
-      <c r="A30" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="34">
-      <c r="A31" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="51">
-      <c r="A32" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="34">
-      <c r="A33" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="51">
-      <c r="A34" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="51">
-      <c r="A35" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="85">
-      <c r="A36" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="51">
-      <c r="A37" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="85">
-      <c r="A38" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="153">
-      <c r="A39" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="85">
-      <c r="A40" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="238">
-      <c r="A41" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="136">
-      <c r="A42" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="136">
-      <c r="A43" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="11">
-        <v>15472</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="85">
-      <c r="A44" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>101</v>
-      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" display="https://www.fishersci.com/us/en/contactus.html" xr:uid="{4BEBABDB-8431-7642-85FA-724157AB25B6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{b67d722d-aa8a-4777-a169-ebeb7a6a3b67}" enabled="0" method="" siteId="{b67d722d-aa8a-4777-a169-ebeb7a6a3b67}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/QuickRegressionTesting5.xlsx
+++ b/QuickRegressionTesting5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thermofisher-my.sharepoint.com/personal/aswathy_n_thermofisher_com/Documents/Aswathy (1)/My_learning/programming_learning/GL_AIML/KeyAreas/GitHub_CICDLearning/RegressionScripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{27A84F89-77DE-E94A-B7B2-4ADE76FB0224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{287D984B-1D2B-8344-9837-7C3E531BB795}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{27A84F89-77DE-E94A-B7B2-4ADE76FB0224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{998848BB-5BD6-874C-B37D-66E1C515465F}"/>
   <bookViews>
-    <workbookView xWindow="44860" yWindow="2860" windowWidth="27720" windowHeight="16940" firstSheet="3" activeTab="4" xr2:uid="{F1B42ADB-BE16-DF45-8356-FD35A5FE073C}"/>
+    <workbookView xWindow="44860" yWindow="2860" windowWidth="27720" windowHeight="16940" firstSheet="3" activeTab="3" xr2:uid="{F1B42ADB-BE16-DF45-8356-FD35A5FE073C}"/>
   </bookViews>
   <sheets>
     <sheet name="URLSheet" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="349">
   <si>
     <t>URL</t>
   </si>
@@ -3526,7 +3526,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3615,28 +3615,44 @@
     <xf numFmtId="49" fontId="15" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3661,37 +3677,22 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6367,13 +6368,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59DE326C-3520-BF47-B048-078953A62B20}">
-  <dimension ref="A1:C287"/>
+  <dimension ref="A1:E287"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="47.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -6384,1599 +6385,1651 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="128" customHeight="1">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:5" ht="128" customHeight="1">
+      <c r="A2" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="49" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="96" customHeight="1">
-      <c r="A3" s="37"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="59"/>
-    </row>
-    <row r="4" spans="1:3" ht="160" customHeight="1">
-      <c r="A4" s="36" t="s">
+    <row r="3" spans="1:5" ht="96" customHeight="1">
+      <c r="A3" s="48"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="50"/>
+    </row>
+    <row r="4" spans="1:5" ht="160" customHeight="1">
+      <c r="A4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="51" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="37"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="61"/>
-    </row>
-    <row r="6" spans="1:3" ht="224" customHeight="1">
-      <c r="A6" s="36" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="48"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="52"/>
+    </row>
+    <row r="6" spans="1:5" ht="224" customHeight="1">
+      <c r="A6" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="51" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="61"/>
-    </row>
-    <row r="8" spans="1:3" ht="64" customHeight="1">
-      <c r="A8" s="36" t="s">
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="48"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="52"/>
+      <c r="E7" s="44"/>
+    </row>
+    <row r="8" spans="1:5" ht="64" customHeight="1">
+      <c r="A8" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="62" t="s">
+      <c r="B8" s="34"/>
+      <c r="C8" s="40" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="335" customHeight="1">
-      <c r="A9" s="39"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="63"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="39"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="63"/>
-    </row>
-    <row r="11" spans="1:3" ht="320" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34" t="s">
+    <row r="9" spans="1:5" ht="335" customHeight="1">
+      <c r="A9" s="47"/>
+      <c r="B9" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="63"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="37"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="64"/>
-    </row>
-    <row r="13" spans="1:3" ht="272" customHeight="1">
-      <c r="A13" s="36" t="s">
+      <c r="C9" s="41"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="47"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="41"/>
+    </row>
+    <row r="11" spans="1:5" ht="320" customHeight="1">
+      <c r="A11" s="47"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="41"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="48"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="42"/>
+    </row>
+    <row r="13" spans="1:5" ht="272" customHeight="1">
+      <c r="A13" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="62" t="s">
+      <c r="B13" s="44"/>
+      <c r="C13" s="40" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="39"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="63"/>
-    </row>
-    <row r="15" spans="1:3" ht="112" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="63"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="39"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="63"/>
+    <row r="14" spans="1:5">
+      <c r="A14" s="47"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="41"/>
+    </row>
+    <row r="15" spans="1:5" ht="112" customHeight="1">
+      <c r="A15" s="47"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="41"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="47"/>
+      <c r="B16" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="41"/>
     </row>
     <row r="17" spans="1:3" ht="48" customHeight="1">
-      <c r="A17" s="39"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="63"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="41"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="39"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="47"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="41"/>
+    </row>
+    <row r="19" spans="1:3" ht="32" customHeight="1">
+      <c r="A19" s="48"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="42"/>
+    </row>
+    <row r="20" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A20" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="40" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="47"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="41"/>
+    </row>
+    <row r="22" spans="1:3" ht="32" customHeight="1">
+      <c r="A22" s="47"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="41"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="47"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="41"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="47"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="41"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="47"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="41"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="47"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="41"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="47"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="41"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="47"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="41"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="47"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="41"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="47"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="41"/>
+    </row>
+    <row r="31" spans="1:3" ht="80" customHeight="1">
+      <c r="A31" s="47"/>
+      <c r="B31" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="63"/>
-    </row>
-    <row r="19" spans="1:3" ht="32" customHeight="1">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="64"/>
-    </row>
-    <row r="20" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A20" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="62" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="39"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="63"/>
-    </row>
-    <row r="22" spans="1:3" ht="32" customHeight="1">
-      <c r="A22" s="39"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="63"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="39"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="63"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="39"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="63"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="39"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="63"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="39"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="63"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="39"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="63"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="39"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="63"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="39"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="63"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="39"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="63"/>
-    </row>
-    <row r="31" spans="1:3" ht="80" customHeight="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="63"/>
+      <c r="C31" s="41"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="39"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="63"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="41"/>
     </row>
     <row r="33" spans="1:3" ht="64" customHeight="1">
-      <c r="A33" s="39"/>
-      <c r="B33" s="34" t="s">
+      <c r="A33" s="47"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="41"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="48"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="42"/>
+    </row>
+    <row r="35" spans="1:3" ht="306" customHeight="1">
+      <c r="A35" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="40" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="47"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="41"/>
+    </row>
+    <row r="37" spans="1:3" ht="32" customHeight="1">
+      <c r="A37" s="47"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="41"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="47"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="41"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="47"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="41"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="47"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="41"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="47"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="41"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="47"/>
+      <c r="B42" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="63"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="64"/>
-    </row>
-    <row r="35" spans="1:3" ht="306" customHeight="1">
-      <c r="A35" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="62" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="39"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="63"/>
-    </row>
-    <row r="37" spans="1:3" ht="32" customHeight="1">
-      <c r="A37" s="39"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="63"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="39"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="63"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="39"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="63"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="39"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="63"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="39"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="63"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="39"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="63"/>
+      <c r="C42" s="41"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="39"/>
-      <c r="B43" s="35"/>
-      <c r="C43" s="63"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="41"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="39"/>
-      <c r="B44" s="34" t="s">
+      <c r="A44" s="47"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="41"/>
+    </row>
+    <row r="45" spans="1:3" ht="64" customHeight="1">
+      <c r="A45" s="48"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="42"/>
+    </row>
+    <row r="46" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A46" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="44"/>
+      <c r="C46" s="40" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="64" customHeight="1">
+      <c r="A47" s="47"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="41"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="47"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="41"/>
+    </row>
+    <row r="49" spans="1:3" ht="48" customHeight="1">
+      <c r="A49" s="47"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="41"/>
+    </row>
+    <row r="50" spans="1:3" ht="48" customHeight="1">
+      <c r="A50" s="47"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="41"/>
+    </row>
+    <row r="51" spans="1:3" ht="32" customHeight="1">
+      <c r="A51" s="47"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="41"/>
+    </row>
+    <row r="52" spans="1:3" ht="48" customHeight="1">
+      <c r="A52" s="47"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="41"/>
+    </row>
+    <row r="53" spans="1:3" ht="48" customHeight="1">
+      <c r="A53" s="47"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="41"/>
+    </row>
+    <row r="54" spans="1:3" ht="32" customHeight="1">
+      <c r="A54" s="47"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="41"/>
+    </row>
+    <row r="55" spans="1:3" ht="64" customHeight="1">
+      <c r="A55" s="47"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="41"/>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="47"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="41"/>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="47"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="41"/>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="47"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="41"/>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="47"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="41"/>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="47"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="41"/>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="47"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="41"/>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="47"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="41"/>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="47"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="41"/>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="47"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="41"/>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="47"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="41"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="47"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="41"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="47"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="41"/>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="47"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="41"/>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="47"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="41"/>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="47"/>
+      <c r="B70" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="63"/>
-    </row>
-    <row r="45" spans="1:3" ht="64" customHeight="1">
-      <c r="A45" s="37"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="64"/>
-    </row>
-    <row r="46" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A46" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="62" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="64" customHeight="1">
-      <c r="A47" s="39"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="63"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="39"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="63"/>
-    </row>
-    <row r="49" spans="1:3" ht="48" customHeight="1">
-      <c r="A49" s="39"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="63"/>
-    </row>
-    <row r="50" spans="1:3" ht="48" customHeight="1">
-      <c r="A50" s="39"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="63"/>
-    </row>
-    <row r="51" spans="1:3" ht="32" customHeight="1">
-      <c r="A51" s="39"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="63"/>
-    </row>
-    <row r="52" spans="1:3" ht="48" customHeight="1">
-      <c r="A52" s="39"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="63"/>
-    </row>
-    <row r="53" spans="1:3" ht="48" customHeight="1">
-      <c r="A53" s="39"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="63"/>
-    </row>
-    <row r="54" spans="1:3" ht="32" customHeight="1">
-      <c r="A54" s="39"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="63"/>
-    </row>
-    <row r="55" spans="1:3" ht="64" customHeight="1">
-      <c r="A55" s="39"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="63"/>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="39"/>
-      <c r="B56" s="38"/>
-      <c r="C56" s="63"/>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="39"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="63"/>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="39"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="63"/>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="39"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="63"/>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="39"/>
-      <c r="B60" s="38"/>
-      <c r="C60" s="63"/>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="39"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="63"/>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="39"/>
-      <c r="B62" s="38"/>
-      <c r="C62" s="63"/>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="39"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="63"/>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="39"/>
-      <c r="B64" s="38"/>
-      <c r="C64" s="63"/>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="39"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="63"/>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="39"/>
-      <c r="B66" s="38"/>
-      <c r="C66" s="63"/>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="39"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="63"/>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="39"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="63"/>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="39"/>
-      <c r="B69" s="38"/>
-      <c r="C69" s="63"/>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="39"/>
-      <c r="B70" s="38"/>
-      <c r="C70" s="63"/>
+      <c r="C70" s="41"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="39"/>
-      <c r="B71" s="35"/>
-      <c r="C71" s="63"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="41"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="39"/>
-      <c r="B72" s="34" t="s">
+      <c r="A72" s="47"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="41"/>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="48"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="42"/>
+    </row>
+    <row r="74" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A74" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" s="44"/>
+      <c r="C74" s="40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="80" customHeight="1">
+      <c r="A75" s="47"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="41"/>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="47"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="41"/>
+    </row>
+    <row r="77" spans="1:3" ht="48" customHeight="1">
+      <c r="A77" s="47"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="41"/>
+    </row>
+    <row r="78" spans="1:3" ht="48" customHeight="1">
+      <c r="A78" s="47"/>
+      <c r="B78" s="44"/>
+      <c r="C78" s="41"/>
+    </row>
+    <row r="79" spans="1:3" ht="48" customHeight="1">
+      <c r="A79" s="47"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="41"/>
+    </row>
+    <row r="80" spans="1:3" ht="32" customHeight="1">
+      <c r="A80" s="47"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="41"/>
+    </row>
+    <row r="81" spans="1:3" ht="64" customHeight="1">
+      <c r="A81" s="47"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="41"/>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="47"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="41"/>
+    </row>
+    <row r="83" spans="1:3" ht="32" customHeight="1">
+      <c r="A83" s="47"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="41"/>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="47"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="41"/>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="47"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="41"/>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="47"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="41"/>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="47"/>
+      <c r="B87" s="44"/>
+      <c r="C87" s="41"/>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="47"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="41"/>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="47"/>
+      <c r="B89" s="44"/>
+      <c r="C89" s="41"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="47"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="41"/>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="47"/>
+      <c r="B91" s="44"/>
+      <c r="C91" s="41"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="47"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="41"/>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="47"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="41"/>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="47"/>
+      <c r="B94" s="44"/>
+      <c r="C94" s="41"/>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="47"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="41"/>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="47"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="41"/>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="47"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="41"/>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="47"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="41"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="47"/>
+      <c r="B99" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C72" s="63"/>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="37"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="64"/>
-    </row>
-    <row r="74" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A74" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="B74" s="38"/>
-      <c r="C74" s="62" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="80" customHeight="1">
-      <c r="A75" s="39"/>
-      <c r="B75" s="38"/>
-      <c r="C75" s="63"/>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="39"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="63"/>
-    </row>
-    <row r="77" spans="1:3" ht="48" customHeight="1">
-      <c r="A77" s="39"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="63"/>
-    </row>
-    <row r="78" spans="1:3" ht="48" customHeight="1">
-      <c r="A78" s="39"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="63"/>
-    </row>
-    <row r="79" spans="1:3" ht="48" customHeight="1">
-      <c r="A79" s="39"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="63"/>
-    </row>
-    <row r="80" spans="1:3" ht="32" customHeight="1">
-      <c r="A80" s="39"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="63"/>
-    </row>
-    <row r="81" spans="1:3" ht="64" customHeight="1">
-      <c r="A81" s="39"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="63"/>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="39"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="63"/>
-    </row>
-    <row r="83" spans="1:3" ht="32" customHeight="1">
-      <c r="A83" s="39"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="63"/>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="39"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="63"/>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="39"/>
-      <c r="B85" s="38"/>
-      <c r="C85" s="63"/>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="39"/>
-      <c r="B86" s="38"/>
-      <c r="C86" s="63"/>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="39"/>
-      <c r="B87" s="38"/>
-      <c r="C87" s="63"/>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="39"/>
-      <c r="B88" s="38"/>
-      <c r="C88" s="63"/>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="39"/>
-      <c r="B89" s="38"/>
-      <c r="C89" s="63"/>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="39"/>
-      <c r="B90" s="38"/>
-      <c r="C90" s="63"/>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="39"/>
-      <c r="B91" s="38"/>
-      <c r="C91" s="63"/>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="39"/>
-      <c r="B92" s="38"/>
-      <c r="C92" s="63"/>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="39"/>
-      <c r="B93" s="38"/>
-      <c r="C93" s="63"/>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="39"/>
-      <c r="B94" s="38"/>
-      <c r="C94" s="63"/>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="39"/>
-      <c r="B95" s="38"/>
-      <c r="C95" s="63"/>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="39"/>
-      <c r="B96" s="38"/>
-      <c r="C96" s="63"/>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="39"/>
-      <c r="B97" s="38"/>
-      <c r="C97" s="63"/>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="39"/>
-      <c r="B98" s="38"/>
-      <c r="C98" s="63"/>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="39"/>
-      <c r="B99" s="38"/>
-      <c r="C99" s="63"/>
+      <c r="C99" s="41"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="39"/>
-      <c r="B100" s="35"/>
-      <c r="C100" s="63"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="41"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="39"/>
-      <c r="B101" s="34" t="s">
+      <c r="A101" s="47"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="41"/>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="48"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="42"/>
+    </row>
+    <row r="103" spans="1:3" ht="409.5" customHeight="1">
+      <c r="A103" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="B103" s="44"/>
+      <c r="C103" s="40" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="80" customHeight="1">
+      <c r="A104" s="47"/>
+      <c r="B104" s="44"/>
+      <c r="C104" s="41"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="47"/>
+      <c r="B105" s="44"/>
+      <c r="C105" s="41"/>
+    </row>
+    <row r="106" spans="1:3" ht="64" customHeight="1">
+      <c r="A106" s="47"/>
+      <c r="B106" s="44"/>
+      <c r="C106" s="41"/>
+    </row>
+    <row r="107" spans="1:3" ht="64" customHeight="1">
+      <c r="A107" s="47"/>
+      <c r="B107" s="44"/>
+      <c r="C107" s="41"/>
+    </row>
+    <row r="108" spans="1:3" ht="48" customHeight="1">
+      <c r="A108" s="47"/>
+      <c r="B108" s="44"/>
+      <c r="C108" s="41"/>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="47"/>
+      <c r="B109" s="44"/>
+      <c r="C109" s="41"/>
+    </row>
+    <row r="110" spans="1:3" ht="32" customHeight="1">
+      <c r="A110" s="47"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="41"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="47"/>
+      <c r="B111" s="44"/>
+      <c r="C111" s="41"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="47"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="41"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="47"/>
+      <c r="B113" s="44"/>
+      <c r="C113" s="41"/>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="47"/>
+      <c r="B114" s="44"/>
+      <c r="C114" s="41"/>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="47"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="41"/>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="47"/>
+      <c r="B116" s="44"/>
+      <c r="C116" s="41"/>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="47"/>
+      <c r="B117" s="44"/>
+      <c r="C117" s="41"/>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="47"/>
+      <c r="B118" s="44"/>
+      <c r="C118" s="41"/>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="47"/>
+      <c r="B119" s="44"/>
+      <c r="C119" s="41"/>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="47"/>
+      <c r="B120" s="44"/>
+      <c r="C120" s="41"/>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="47"/>
+      <c r="B121" s="44"/>
+      <c r="C121" s="41"/>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="47"/>
+      <c r="B122" s="44"/>
+      <c r="C122" s="41"/>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="47"/>
+      <c r="B123" s="44"/>
+      <c r="C123" s="41"/>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="47"/>
+      <c r="B124" s="45"/>
+      <c r="C124" s="41"/>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="47"/>
+      <c r="B125" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C101" s="63"/>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="37"/>
-      <c r="B102" s="38"/>
-      <c r="C102" s="64"/>
-    </row>
-    <row r="103" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A103" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="B103" s="38"/>
-      <c r="C103" s="62" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="80" customHeight="1">
-      <c r="A104" s="39"/>
-      <c r="B104" s="38"/>
-      <c r="C104" s="63"/>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="39"/>
-      <c r="B105" s="38"/>
-      <c r="C105" s="63"/>
-    </row>
-    <row r="106" spans="1:3" ht="64" customHeight="1">
-      <c r="A106" s="39"/>
-      <c r="B106" s="38"/>
-      <c r="C106" s="63"/>
-    </row>
-    <row r="107" spans="1:3" ht="64" customHeight="1">
-      <c r="A107" s="39"/>
-      <c r="B107" s="38"/>
-      <c r="C107" s="63"/>
-    </row>
-    <row r="108" spans="1:3" ht="48" customHeight="1">
-      <c r="A108" s="39"/>
-      <c r="B108" s="38"/>
-      <c r="C108" s="63"/>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="39"/>
-      <c r="B109" s="38"/>
-      <c r="C109" s="63"/>
-    </row>
-    <row r="110" spans="1:3" ht="32" customHeight="1">
-      <c r="A110" s="39"/>
-      <c r="B110" s="38"/>
-      <c r="C110" s="63"/>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="39"/>
-      <c r="B111" s="38"/>
-      <c r="C111" s="63"/>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="39"/>
-      <c r="B112" s="38"/>
-      <c r="C112" s="63"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="39"/>
-      <c r="B113" s="38"/>
-      <c r="C113" s="63"/>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="39"/>
-      <c r="B114" s="38"/>
-      <c r="C114" s="63"/>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="39"/>
-      <c r="B115" s="38"/>
-      <c r="C115" s="63"/>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="39"/>
-      <c r="B116" s="38"/>
-      <c r="C116" s="63"/>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="39"/>
-      <c r="B117" s="38"/>
-      <c r="C117" s="63"/>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="39"/>
-      <c r="B118" s="38"/>
-      <c r="C118" s="63"/>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="39"/>
-      <c r="B119" s="38"/>
-      <c r="C119" s="63"/>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="39"/>
-      <c r="B120" s="38"/>
-      <c r="C120" s="63"/>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="39"/>
-      <c r="B121" s="38"/>
-      <c r="C121" s="63"/>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="39"/>
-      <c r="B122" s="38"/>
-      <c r="C122" s="63"/>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="39"/>
-      <c r="B123" s="38"/>
-      <c r="C123" s="63"/>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="39"/>
-      <c r="B124" s="38"/>
-      <c r="C124" s="63"/>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="39"/>
-      <c r="B125" s="38"/>
-      <c r="C125" s="63"/>
+      <c r="C125" s="41"/>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="39"/>
-      <c r="B126" s="35"/>
-      <c r="C126" s="63"/>
+      <c r="A126" s="47"/>
+      <c r="B126" s="44"/>
+      <c r="C126" s="41"/>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="39"/>
-      <c r="B127" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C127" s="63"/>
+      <c r="A127" s="47"/>
+      <c r="B127" s="44"/>
+      <c r="C127" s="41"/>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="37"/>
-      <c r="B128" s="38"/>
-      <c r="C128" s="64"/>
+      <c r="A128" s="48"/>
+      <c r="B128" s="44"/>
+      <c r="C128" s="42"/>
     </row>
     <row r="129" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A129" s="36" t="s">
+      <c r="A129" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="B129" s="38"/>
-      <c r="C129" s="62" t="s">
+      <c r="B129" s="44"/>
+      <c r="C129" s="40" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="80" customHeight="1">
-      <c r="A130" s="39"/>
-      <c r="B130" s="38"/>
-      <c r="C130" s="63"/>
+      <c r="A130" s="47"/>
+      <c r="B130" s="44"/>
+      <c r="C130" s="41"/>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="39"/>
-      <c r="B131" s="38"/>
-      <c r="C131" s="63"/>
+      <c r="A131" s="47"/>
+      <c r="B131" s="44"/>
+      <c r="C131" s="41"/>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="39"/>
-      <c r="B132" s="38"/>
-      <c r="C132" s="63"/>
+      <c r="A132" s="47"/>
+      <c r="B132" s="44"/>
+      <c r="C132" s="41"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="39"/>
-      <c r="B133" s="38"/>
-      <c r="C133" s="63"/>
+      <c r="A133" s="47"/>
+      <c r="B133" s="44"/>
+      <c r="C133" s="41"/>
     </row>
     <row r="134" spans="1:3" ht="48" customHeight="1">
-      <c r="A134" s="39"/>
-      <c r="B134" s="38"/>
-      <c r="C134" s="63"/>
+      <c r="A134" s="47"/>
+      <c r="B134" s="44"/>
+      <c r="C134" s="41"/>
     </row>
     <row r="135" spans="1:3" ht="80" customHeight="1">
-      <c r="A135" s="39"/>
-      <c r="B135" s="38"/>
-      <c r="C135" s="63"/>
+      <c r="A135" s="47"/>
+      <c r="B135" s="44"/>
+      <c r="C135" s="41"/>
     </row>
     <row r="136" spans="1:3" ht="64" customHeight="1">
-      <c r="A136" s="39"/>
-      <c r="B136" s="38"/>
-      <c r="C136" s="63"/>
+      <c r="A136" s="47"/>
+      <c r="B136" s="44"/>
+      <c r="C136" s="41"/>
     </row>
     <row r="137" spans="1:3" ht="32" customHeight="1">
-      <c r="A137" s="39"/>
-      <c r="B137" s="38"/>
-      <c r="C137" s="63"/>
+      <c r="A137" s="47"/>
+      <c r="B137" s="45"/>
+      <c r="C137" s="41"/>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="39"/>
-      <c r="B138" s="38"/>
-      <c r="C138" s="63"/>
+      <c r="A138" s="47"/>
+      <c r="B138" s="61">
+        <v>11012044</v>
+      </c>
+      <c r="C138" s="41"/>
     </row>
     <row r="139" spans="1:3" ht="80" customHeight="1">
-      <c r="A139" s="39"/>
-      <c r="B139" s="35"/>
-      <c r="C139" s="63"/>
+      <c r="A139" s="47"/>
+      <c r="B139" s="62"/>
+      <c r="C139" s="41"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="39"/>
-      <c r="B140" s="55">
-        <v>11012044</v>
-      </c>
-      <c r="C140" s="63"/>
+      <c r="A140" s="47"/>
+      <c r="B140" s="62"/>
+      <c r="C140" s="41"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="37"/>
-      <c r="B141" s="56"/>
-      <c r="C141" s="64"/>
+      <c r="A141" s="48"/>
+      <c r="B141" s="62"/>
+      <c r="C141" s="42"/>
     </row>
     <row r="142" spans="1:3" ht="404" customHeight="1">
-      <c r="A142" s="36" t="s">
+      <c r="A142" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="B142" s="56"/>
-      <c r="C142" s="62" t="s">
+      <c r="B142" s="62"/>
+      <c r="C142" s="40" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="64" customHeight="1">
-      <c r="A143" s="39"/>
-      <c r="B143" s="56"/>
-      <c r="C143" s="63"/>
+      <c r="A143" s="47"/>
+      <c r="B143" s="62"/>
+      <c r="C143" s="41"/>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="39"/>
-      <c r="B144" s="56"/>
-      <c r="C144" s="63"/>
+      <c r="A144" s="47"/>
+      <c r="B144" s="62"/>
+      <c r="C144" s="41"/>
     </row>
     <row r="145" spans="1:3" ht="64" customHeight="1">
-      <c r="A145" s="39"/>
-      <c r="B145" s="56"/>
-      <c r="C145" s="63"/>
+      <c r="A145" s="47"/>
+      <c r="B145" s="62"/>
+      <c r="C145" s="41"/>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="39"/>
-      <c r="B146" s="56"/>
-      <c r="C146" s="63"/>
+      <c r="A146" s="47"/>
+      <c r="B146" s="62"/>
+      <c r="C146" s="41"/>
     </row>
     <row r="147" spans="1:3" ht="32" customHeight="1">
-      <c r="A147" s="39"/>
-      <c r="B147" s="56"/>
-      <c r="C147" s="63"/>
+      <c r="A147" s="47"/>
+      <c r="B147" s="62"/>
+      <c r="C147" s="41"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="39"/>
-      <c r="B148" s="56"/>
-      <c r="C148" s="63"/>
+      <c r="A148" s="47"/>
+      <c r="B148" s="62"/>
+      <c r="C148" s="41"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="39"/>
-      <c r="B149" s="56"/>
-      <c r="C149" s="63"/>
+      <c r="A149" s="47"/>
+      <c r="B149" s="62"/>
+      <c r="C149" s="41"/>
     </row>
     <row r="150" spans="1:3">
-      <c r="A150" s="39"/>
-      <c r="B150" s="56"/>
-      <c r="C150" s="63"/>
+      <c r="A150" s="47"/>
+      <c r="B150" s="62"/>
+      <c r="C150" s="41"/>
     </row>
     <row r="151" spans="1:3">
-      <c r="A151" s="39"/>
-      <c r="B151" s="56"/>
-      <c r="C151" s="63"/>
+      <c r="A151" s="47"/>
+      <c r="B151" s="62"/>
+      <c r="C151" s="41"/>
     </row>
     <row r="152" spans="1:3">
-      <c r="A152" s="39"/>
-      <c r="B152" s="56"/>
-      <c r="C152" s="63"/>
+      <c r="A152" s="47"/>
+      <c r="B152" s="62"/>
+      <c r="C152" s="41"/>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="39"/>
-      <c r="B153" s="56"/>
-      <c r="C153" s="63"/>
+      <c r="A153" s="47"/>
+      <c r="B153" s="63"/>
+      <c r="C153" s="41"/>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="39"/>
-      <c r="B154" s="56"/>
-      <c r="C154" s="63"/>
+      <c r="A154" s="47"/>
+      <c r="B154" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C154" s="41"/>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155" s="39"/>
-      <c r="B155" s="57"/>
-      <c r="C155" s="63"/>
+      <c r="A155" s="47"/>
+      <c r="B155" s="44"/>
+      <c r="C155" s="41"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="39"/>
-      <c r="B156" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C156" s="63"/>
+      <c r="A156" s="47"/>
+      <c r="B156" s="45"/>
+      <c r="C156" s="41"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="37"/>
-      <c r="B157" s="38"/>
-      <c r="C157" s="64"/>
+      <c r="A157" s="48"/>
+      <c r="B157" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C157" s="42"/>
     </row>
     <row r="158" spans="1:3" ht="68" customHeight="1">
-      <c r="A158" s="36" t="s">
+      <c r="A158" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B158" s="35"/>
-      <c r="C158" s="62" t="s">
+      <c r="B158" s="45"/>
+      <c r="C158" s="40" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="32" customHeight="1">
-      <c r="A159" s="39"/>
-      <c r="B159" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C159" s="63"/>
+      <c r="A159" s="47"/>
+      <c r="B159" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C159" s="41"/>
     </row>
     <row r="160" spans="1:3">
-      <c r="A160" s="37"/>
-      <c r="B160" s="35"/>
-      <c r="C160" s="64"/>
+      <c r="A160" s="48"/>
+      <c r="B160" s="44"/>
+      <c r="C160" s="42"/>
     </row>
     <row r="161" spans="1:3" ht="32" customHeight="1">
-      <c r="A161" s="45" t="s">
+      <c r="A161" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B161" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C161" s="65" t="s">
+      <c r="B161" s="44"/>
+      <c r="C161" s="38" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="46"/>
-      <c r="B162" s="38"/>
-      <c r="C162" s="66"/>
+      <c r="A162" s="70"/>
+      <c r="B162" s="44"/>
+      <c r="C162" s="39"/>
     </row>
     <row r="163" spans="1:3" ht="221" customHeight="1">
-      <c r="A163" s="36" t="s">
+      <c r="A163" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B163" s="38"/>
-      <c r="C163" s="62" t="s">
+      <c r="B163" s="44"/>
+      <c r="C163" s="40" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="48" customHeight="1">
-      <c r="A164" s="39"/>
-      <c r="B164" s="38"/>
-      <c r="C164" s="63"/>
+      <c r="A164" s="47"/>
+      <c r="B164" s="44"/>
+      <c r="C164" s="41"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="39"/>
-      <c r="B165" s="38"/>
-      <c r="C165" s="63"/>
+      <c r="A165" s="47"/>
+      <c r="B165" s="44"/>
+      <c r="C165" s="41"/>
     </row>
     <row r="166" spans="1:3">
-      <c r="A166" s="39"/>
-      <c r="B166" s="38"/>
-      <c r="C166" s="63"/>
+      <c r="A166" s="47"/>
+      <c r="B166" s="44"/>
+      <c r="C166" s="41"/>
     </row>
     <row r="167" spans="1:3" ht="32" customHeight="1">
-      <c r="A167" s="39"/>
-      <c r="B167" s="38"/>
-      <c r="C167" s="63"/>
+      <c r="A167" s="47"/>
+      <c r="B167" s="44"/>
+      <c r="C167" s="41"/>
     </row>
     <row r="168" spans="1:3" ht="32" customHeight="1">
-      <c r="A168" s="39"/>
-      <c r="B168" s="38"/>
-      <c r="C168" s="63"/>
+      <c r="A168" s="47"/>
+      <c r="B168" s="45"/>
+      <c r="C168" s="41"/>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="39"/>
-      <c r="B169" s="38"/>
-      <c r="C169" s="63"/>
+      <c r="A169" s="47"/>
+      <c r="B169" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C169" s="41"/>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="39"/>
-      <c r="B170" s="35"/>
-      <c r="C170" s="63"/>
+      <c r="A170" s="47"/>
+      <c r="B170" s="44"/>
+      <c r="C170" s="41"/>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171" s="39"/>
-      <c r="B171" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C171" s="63"/>
+      <c r="A171" s="47"/>
+      <c r="B171" s="44"/>
+      <c r="C171" s="41"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="37"/>
-      <c r="B172" s="38"/>
-      <c r="C172" s="64"/>
+      <c r="A172" s="48"/>
+      <c r="B172" s="44"/>
+      <c r="C172" s="42"/>
     </row>
     <row r="173" spans="1:3" ht="238" customHeight="1">
-      <c r="A173" s="42" t="s">
+      <c r="A173" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B173" s="38"/>
-      <c r="C173" s="62" t="s">
+      <c r="B173" s="44"/>
+      <c r="C173" s="40" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="32" customHeight="1">
-      <c r="A174" s="43"/>
-      <c r="B174" s="38"/>
-      <c r="C174" s="63"/>
+      <c r="A174" s="67"/>
+      <c r="B174" s="44"/>
+      <c r="C174" s="41"/>
     </row>
     <row r="175" spans="1:3">
-      <c r="A175" s="43"/>
-      <c r="B175" s="38"/>
-      <c r="C175" s="63"/>
+      <c r="A175" s="67"/>
+      <c r="B175" s="45"/>
+      <c r="C175" s="41"/>
     </row>
     <row r="176" spans="1:3" ht="32" customHeight="1">
-      <c r="A176" s="43"/>
-      <c r="B176" s="38"/>
-      <c r="C176" s="63"/>
+      <c r="A176" s="67"/>
+      <c r="B176" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" s="41"/>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="43"/>
-      <c r="B177" s="35"/>
-      <c r="C177" s="63"/>
+      <c r="A177" s="67"/>
+      <c r="B177" s="44"/>
+      <c r="C177" s="41"/>
     </row>
     <row r="178" spans="1:3" ht="64" customHeight="1">
-      <c r="A178" s="43"/>
-      <c r="B178" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C178" s="63"/>
+      <c r="A178" s="67"/>
+      <c r="B178" s="44"/>
+      <c r="C178" s="41"/>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179" s="44"/>
-      <c r="B179" s="38"/>
-      <c r="C179" s="64"/>
+      <c r="A179" s="68"/>
+      <c r="B179" s="44"/>
+      <c r="C179" s="42"/>
     </row>
     <row r="180" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A180" s="36" t="s">
+      <c r="A180" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B180" s="38"/>
-      <c r="C180" s="62" t="s">
+      <c r="B180" s="44"/>
+      <c r="C180" s="40" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="48" customHeight="1">
-      <c r="A181" s="39"/>
-      <c r="B181" s="38"/>
-      <c r="C181" s="63"/>
+      <c r="A181" s="47"/>
+      <c r="B181" s="44"/>
+      <c r="C181" s="41"/>
     </row>
     <row r="182" spans="1:3">
-      <c r="A182" s="39"/>
-      <c r="B182" s="38"/>
-      <c r="C182" s="63"/>
+      <c r="A182" s="47"/>
+      <c r="B182" s="44"/>
+      <c r="C182" s="41"/>
     </row>
     <row r="183" spans="1:3" ht="64" customHeight="1">
-      <c r="A183" s="39"/>
-      <c r="B183" s="38"/>
-      <c r="C183" s="63"/>
+      <c r="A183" s="47"/>
+      <c r="B183" s="44"/>
+      <c r="C183" s="41"/>
     </row>
     <row r="184" spans="1:3">
-      <c r="A184" s="39"/>
-      <c r="B184" s="38"/>
-      <c r="C184" s="63"/>
+      <c r="A184" s="47"/>
+      <c r="B184" s="44"/>
+      <c r="C184" s="41"/>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="39"/>
-      <c r="B185" s="38"/>
-      <c r="C185" s="63"/>
+      <c r="A185" s="47"/>
+      <c r="B185" s="44"/>
+      <c r="C185" s="41"/>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="39"/>
-      <c r="B186" s="38"/>
-      <c r="C186" s="63"/>
+      <c r="A186" s="47"/>
+      <c r="B186" s="44"/>
+      <c r="C186" s="41"/>
     </row>
     <row r="187" spans="1:3">
-      <c r="A187" s="39"/>
-      <c r="B187" s="38"/>
-      <c r="C187" s="63"/>
+      <c r="A187" s="47"/>
+      <c r="B187" s="44"/>
+      <c r="C187" s="41"/>
     </row>
     <row r="188" spans="1:3">
-      <c r="A188" s="39"/>
-      <c r="B188" s="38"/>
-      <c r="C188" s="63"/>
+      <c r="A188" s="47"/>
+      <c r="B188" s="44"/>
+      <c r="C188" s="41"/>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="39"/>
-      <c r="B189" s="38"/>
-      <c r="C189" s="63"/>
+      <c r="A189" s="47"/>
+      <c r="B189" s="44"/>
+      <c r="C189" s="41"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="39"/>
-      <c r="B190" s="38"/>
-      <c r="C190" s="63"/>
+      <c r="A190" s="47"/>
+      <c r="B190" s="44"/>
+      <c r="C190" s="41"/>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="39"/>
-      <c r="B191" s="38"/>
-      <c r="C191" s="63"/>
+      <c r="A191" s="47"/>
+      <c r="B191" s="44"/>
+      <c r="C191" s="41"/>
     </row>
     <row r="192" spans="1:3">
-      <c r="A192" s="39"/>
-      <c r="B192" s="38"/>
-      <c r="C192" s="63"/>
+      <c r="A192" s="47"/>
+      <c r="B192" s="44"/>
+      <c r="C192" s="41"/>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="39"/>
-      <c r="B193" s="38"/>
-      <c r="C193" s="63"/>
+      <c r="A193" s="47"/>
+      <c r="B193" s="44"/>
+      <c r="C193" s="41"/>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="39"/>
-      <c r="B194" s="38"/>
-      <c r="C194" s="63"/>
+      <c r="A194" s="47"/>
+      <c r="B194" s="44"/>
+      <c r="C194" s="41"/>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="39"/>
-      <c r="B195" s="38"/>
-      <c r="C195" s="63"/>
+      <c r="A195" s="47"/>
+      <c r="B195" s="44"/>
+      <c r="C195" s="41"/>
     </row>
     <row r="196" spans="1:3">
-      <c r="A196" s="39"/>
-      <c r="B196" s="38"/>
-      <c r="C196" s="63"/>
+      <c r="A196" s="47"/>
+      <c r="B196" s="44"/>
+      <c r="C196" s="41"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="39"/>
-      <c r="B197" s="38"/>
-      <c r="C197" s="63"/>
+      <c r="A197" s="47"/>
+      <c r="B197" s="45"/>
+      <c r="C197" s="41"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="39"/>
-      <c r="B198" s="38"/>
-      <c r="C198" s="63"/>
+      <c r="A198" s="47"/>
+      <c r="B198" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C198" s="41"/>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="39"/>
-      <c r="B199" s="35"/>
-      <c r="C199" s="63"/>
+      <c r="A199" s="47"/>
+      <c r="B199" s="45"/>
+      <c r="C199" s="41"/>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="39"/>
-      <c r="B200" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C200" s="63"/>
+      <c r="A200" s="47"/>
+      <c r="B200" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C200" s="41"/>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201" s="37"/>
-      <c r="B201" s="35"/>
-      <c r="C201" s="64"/>
+      <c r="A201" s="48"/>
+      <c r="B201" s="44"/>
+      <c r="C201" s="42"/>
     </row>
     <row r="202" spans="1:3" ht="48" customHeight="1">
-      <c r="A202" s="36" t="s">
+      <c r="A202" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B202" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C202" s="65" t="s">
+      <c r="B202" s="44"/>
+      <c r="C202" s="38" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="37"/>
-      <c r="B203" s="38"/>
-      <c r="C203" s="66"/>
+      <c r="A203" s="48"/>
+      <c r="B203" s="44"/>
+      <c r="C203" s="39"/>
     </row>
     <row r="204" spans="1:3" ht="255" customHeight="1">
-      <c r="A204" s="36" t="s">
+      <c r="A204" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B204" s="38"/>
-      <c r="C204" s="62" t="s">
+      <c r="B204" s="44"/>
+      <c r="C204" s="40" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="96" customHeight="1">
-      <c r="A205" s="39"/>
-      <c r="B205" s="38"/>
-      <c r="C205" s="63"/>
+      <c r="A205" s="47"/>
+      <c r="B205" s="44"/>
+      <c r="C205" s="41"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="39"/>
-      <c r="B206" s="38"/>
-      <c r="C206" s="63"/>
+      <c r="A206" s="47"/>
+      <c r="B206" s="44"/>
+      <c r="C206" s="41"/>
     </row>
     <row r="207" spans="1:3" ht="32" customHeight="1">
-      <c r="A207" s="39"/>
-      <c r="B207" s="38"/>
-      <c r="C207" s="63"/>
+      <c r="A207" s="47"/>
+      <c r="B207" s="45"/>
+      <c r="C207" s="41"/>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="39"/>
-      <c r="B208" s="38"/>
-      <c r="C208" s="63"/>
+      <c r="A208" s="47"/>
+      <c r="B208" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C208" s="41"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="39"/>
-      <c r="B209" s="35"/>
-      <c r="C209" s="63"/>
+      <c r="A209" s="47"/>
+      <c r="B209" s="44"/>
+      <c r="C209" s="41"/>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="39"/>
-      <c r="B210" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C210" s="63"/>
+      <c r="A210" s="47"/>
+      <c r="B210" s="44"/>
+      <c r="C210" s="41"/>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="37"/>
-      <c r="B211" s="38"/>
-      <c r="C211" s="64"/>
+      <c r="A211" s="48"/>
+      <c r="B211" s="44"/>
+      <c r="C211" s="42"/>
     </row>
     <row r="212" spans="1:3" ht="255" customHeight="1">
-      <c r="A212" s="36" t="s">
+      <c r="A212" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="B212" s="38"/>
-      <c r="C212" s="62" t="s">
+      <c r="B212" s="44"/>
+      <c r="C212" s="40" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="39"/>
-      <c r="B213" s="38"/>
-      <c r="C213" s="63"/>
+      <c r="A213" s="47"/>
+      <c r="B213" s="44"/>
+      <c r="C213" s="41"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="39"/>
-      <c r="B214" s="38"/>
-      <c r="C214" s="63"/>
+      <c r="A214" s="47"/>
+      <c r="B214" s="44"/>
+      <c r="C214" s="41"/>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="39"/>
-      <c r="B215" s="38"/>
-      <c r="C215" s="63"/>
+      <c r="A215" s="47"/>
+      <c r="B215" s="44"/>
+      <c r="C215" s="41"/>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="39"/>
-      <c r="B216" s="38"/>
-      <c r="C216" s="63"/>
+      <c r="A216" s="47"/>
+      <c r="B216" s="44"/>
+      <c r="C216" s="41"/>
     </row>
     <row r="217" spans="1:3">
-      <c r="A217" s="39"/>
-      <c r="B217" s="38"/>
-      <c r="C217" s="63"/>
+      <c r="A217" s="47"/>
+      <c r="B217" s="44"/>
+      <c r="C217" s="41"/>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="39"/>
-      <c r="B218" s="38"/>
-      <c r="C218" s="63"/>
+      <c r="A218" s="47"/>
+      <c r="B218" s="44"/>
+      <c r="C218" s="41"/>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="39"/>
-      <c r="B219" s="38"/>
-      <c r="C219" s="63"/>
+      <c r="A219" s="47"/>
+      <c r="B219" s="45"/>
+      <c r="C219" s="41"/>
     </row>
     <row r="220" spans="1:3">
-      <c r="A220" s="39"/>
-      <c r="B220" s="38"/>
-      <c r="C220" s="63"/>
+      <c r="A220" s="47"/>
+      <c r="B220" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C220" s="41"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="39"/>
-      <c r="B221" s="35"/>
-      <c r="C221" s="63"/>
+      <c r="A221" s="47"/>
+      <c r="B221" s="44"/>
+      <c r="C221" s="41"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="39"/>
-      <c r="B222" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C222" s="63"/>
+      <c r="A222" s="47"/>
+      <c r="B222" s="44"/>
+      <c r="C222" s="41"/>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="37"/>
-      <c r="B223" s="38"/>
-      <c r="C223" s="64"/>
+      <c r="A223" s="48"/>
+      <c r="B223" s="45"/>
+      <c r="C223" s="42"/>
     </row>
     <row r="224" spans="1:3" ht="102" customHeight="1">
-      <c r="A224" s="36" t="s">
+      <c r="A224" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B224" s="38"/>
-      <c r="C224" s="62" t="s">
+      <c r="B224" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C224" s="40" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="48" customHeight="1">
-      <c r="A225" s="39"/>
-      <c r="B225" s="35"/>
-      <c r="C225" s="63"/>
+      <c r="A225" s="47"/>
+      <c r="B225" s="44"/>
+      <c r="C225" s="41"/>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="39"/>
-      <c r="B226" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C226" s="63"/>
+      <c r="A226" s="47"/>
+      <c r="B226" s="44"/>
+      <c r="C226" s="41"/>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="37"/>
-      <c r="B227" s="38"/>
-      <c r="C227" s="64"/>
+      <c r="A227" s="48"/>
+      <c r="B227" s="44"/>
+      <c r="C227" s="42"/>
     </row>
     <row r="228" spans="1:3" ht="409.5" customHeight="1">
-      <c r="A228" s="36" t="s">
+      <c r="A228" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="B228" s="38"/>
-      <c r="C228" s="62" t="s">
+      <c r="B228" s="44"/>
+      <c r="C228" s="40" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="32" customHeight="1">
-      <c r="A229" s="39"/>
-      <c r="B229" s="38"/>
-      <c r="C229" s="63"/>
+      <c r="A229" s="47"/>
+      <c r="B229" s="44"/>
+      <c r="C229" s="41"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="39"/>
-      <c r="B230" s="38"/>
-      <c r="C230" s="63"/>
+      <c r="A230" s="47"/>
+      <c r="B230" s="44"/>
+      <c r="C230" s="41"/>
     </row>
     <row r="231" spans="1:3" ht="48" customHeight="1">
-      <c r="A231" s="39"/>
-      <c r="B231" s="38"/>
-      <c r="C231" s="63"/>
+      <c r="A231" s="47"/>
+      <c r="B231" s="44"/>
+      <c r="C231" s="41"/>
     </row>
     <row r="232" spans="1:3" ht="48" customHeight="1">
-      <c r="A232" s="39"/>
-      <c r="B232" s="38"/>
-      <c r="C232" s="63"/>
+      <c r="A232" s="47"/>
+      <c r="B232" s="44"/>
+      <c r="C232" s="41"/>
     </row>
     <row r="233" spans="1:3" ht="64" customHeight="1">
-      <c r="A233" s="39"/>
-      <c r="B233" s="38"/>
-      <c r="C233" s="63"/>
+      <c r="A233" s="47"/>
+      <c r="B233" s="44"/>
+      <c r="C233" s="41"/>
     </row>
     <row r="234" spans="1:3" ht="48" customHeight="1">
-      <c r="A234" s="39"/>
-      <c r="B234" s="38"/>
-      <c r="C234" s="63"/>
+      <c r="A234" s="47"/>
+      <c r="B234" s="44"/>
+      <c r="C234" s="41"/>
     </row>
     <row r="235" spans="1:3" ht="48" customHeight="1">
-      <c r="A235" s="39"/>
-      <c r="B235" s="38"/>
-      <c r="C235" s="63"/>
+      <c r="A235" s="47"/>
+      <c r="B235" s="44"/>
+      <c r="C235" s="41"/>
     </row>
     <row r="236" spans="1:3">
-      <c r="A236" s="39"/>
-      <c r="B236" s="38"/>
-      <c r="C236" s="63"/>
+      <c r="A236" s="47"/>
+      <c r="B236" s="44"/>
+      <c r="C236" s="41"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="39"/>
-      <c r="B237" s="38"/>
-      <c r="C237" s="63"/>
+      <c r="A237" s="47"/>
+      <c r="B237" s="44"/>
+      <c r="C237" s="41"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="39"/>
-      <c r="B238" s="38"/>
-      <c r="C238" s="63"/>
+      <c r="A238" s="47"/>
+      <c r="B238" s="44"/>
+      <c r="C238" s="41"/>
     </row>
     <row r="239" spans="1:3" ht="32" customHeight="1">
-      <c r="A239" s="39"/>
-      <c r="B239" s="38"/>
-      <c r="C239" s="63"/>
+      <c r="A239" s="47"/>
+      <c r="B239" s="44"/>
+      <c r="C239" s="41"/>
     </row>
     <row r="240" spans="1:3" ht="32" customHeight="1">
-      <c r="A240" s="39"/>
-      <c r="B240" s="38"/>
-      <c r="C240" s="63"/>
+      <c r="A240" s="47"/>
+      <c r="B240" s="45"/>
+      <c r="C240" s="41"/>
     </row>
     <row r="241" spans="1:3" ht="32" customHeight="1">
-      <c r="A241" s="39"/>
-      <c r="B241" s="38"/>
-      <c r="C241" s="63"/>
+      <c r="A241" s="47"/>
+      <c r="B241" s="53">
+        <v>15472</v>
+      </c>
+      <c r="C241" s="41"/>
     </row>
     <row r="242" spans="1:3" ht="32" customHeight="1">
-      <c r="A242" s="39"/>
-      <c r="B242" s="35"/>
-      <c r="C242" s="63"/>
+      <c r="A242" s="47"/>
+      <c r="B242" s="54"/>
+      <c r="C242" s="41"/>
     </row>
     <row r="243" spans="1:3" ht="32" customHeight="1">
-      <c r="A243" s="39"/>
-      <c r="B243" s="47">
-        <v>15472</v>
-      </c>
-      <c r="C243" s="63"/>
+      <c r="A243" s="47"/>
+      <c r="B243" s="54"/>
+      <c r="C243" s="41"/>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244" s="37"/>
-      <c r="B244" s="48"/>
-      <c r="C244" s="64"/>
+      <c r="A244" s="48"/>
+      <c r="B244" s="54"/>
+      <c r="C244" s="42"/>
     </row>
     <row r="245" spans="1:3" ht="289" customHeight="1">
-      <c r="A245" s="50" t="s">
+      <c r="A245" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="B245" s="48"/>
-      <c r="C245" s="62" t="s">
+      <c r="B245" s="54"/>
+      <c r="C245" s="40" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="80" customHeight="1">
-      <c r="A246" s="51"/>
-      <c r="B246" s="48"/>
-      <c r="C246" s="63"/>
+      <c r="A246" s="57"/>
+      <c r="B246" s="54"/>
+      <c r="C246" s="41"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="51"/>
-      <c r="B247" s="48"/>
-      <c r="C247" s="63"/>
+      <c r="A247" s="57"/>
+      <c r="B247" s="54"/>
+      <c r="C247" s="41"/>
     </row>
     <row r="248" spans="1:3">
-      <c r="A248" s="51"/>
-      <c r="B248" s="48"/>
-      <c r="C248" s="63"/>
+      <c r="A248" s="57"/>
+      <c r="B248" s="54"/>
+      <c r="C248" s="41"/>
     </row>
     <row r="249" spans="1:3">
-      <c r="A249" s="51"/>
-      <c r="B249" s="48"/>
-      <c r="C249" s="63"/>
+      <c r="A249" s="57"/>
+      <c r="B249" s="54"/>
+      <c r="C249" s="41"/>
     </row>
     <row r="250" spans="1:3" ht="32" customHeight="1">
-      <c r="A250" s="51"/>
-      <c r="B250" s="48"/>
-      <c r="C250" s="63"/>
+      <c r="A250" s="57"/>
+      <c r="B250" s="55"/>
+      <c r="C250" s="41"/>
     </row>
     <row r="251" spans="1:3" ht="32" customHeight="1">
-      <c r="A251" s="51"/>
-      <c r="B251" s="48"/>
-      <c r="C251" s="63"/>
+      <c r="A251" s="57"/>
+      <c r="B251" s="59">
+        <v>75009240</v>
+      </c>
+      <c r="C251" s="41"/>
     </row>
     <row r="252" spans="1:3" ht="32" customHeight="1">
-      <c r="A252" s="51"/>
-      <c r="B252" s="49"/>
-      <c r="C252" s="63"/>
+      <c r="A252" s="57"/>
+      <c r="B252" s="60"/>
+      <c r="C252" s="41"/>
     </row>
     <row r="253" spans="1:3">
-      <c r="A253" s="51"/>
-      <c r="B253" s="53">
-        <v>75009240</v>
-      </c>
-      <c r="C253" s="63"/>
+      <c r="A253" s="57"/>
+      <c r="B253" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="C253" s="41"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="52"/>
-      <c r="B254" s="54"/>
-      <c r="C254" s="64"/>
+      <c r="A254" s="58"/>
+      <c r="B254" s="44"/>
+      <c r="C254" s="42"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="40" t="s">
+      <c r="A255" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="B255" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="C255" s="65" t="s">
+      <c r="B255" s="44"/>
+      <c r="C255" s="38" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="256" spans="1:3">
-      <c r="A256" s="41"/>
-      <c r="B256" s="38"/>
-      <c r="C256" s="66"/>
+      <c r="A256" s="65"/>
+      <c r="B256" s="44"/>
+      <c r="C256" s="39"/>
     </row>
     <row r="257" spans="1:3" ht="388" customHeight="1">
-      <c r="A257" s="36" t="s">
+      <c r="A257" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="B257" s="38"/>
-      <c r="C257" s="62" t="s">
+      <c r="B257" s="44"/>
+      <c r="C257" s="40" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="258" spans="1:3">
-      <c r="A258" s="39"/>
-      <c r="B258" s="38"/>
-      <c r="C258" s="63"/>
+      <c r="A258" s="47"/>
+      <c r="B258" s="44"/>
+      <c r="C258" s="41"/>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="39"/>
-      <c r="B259" s="38"/>
-      <c r="C259" s="63"/>
+      <c r="A259" s="47"/>
+      <c r="B259" s="44"/>
+      <c r="C259" s="41"/>
     </row>
     <row r="260" spans="1:3" ht="48" customHeight="1">
-      <c r="A260" s="39"/>
-      <c r="B260" s="38"/>
-      <c r="C260" s="63"/>
+      <c r="A260" s="47"/>
+      <c r="B260" s="44"/>
+      <c r="C260" s="41"/>
     </row>
     <row r="261" spans="1:3" ht="32" customHeight="1">
-      <c r="A261" s="39"/>
-      <c r="B261" s="38"/>
-      <c r="C261" s="63"/>
+      <c r="A261" s="47"/>
+      <c r="B261" s="44"/>
+      <c r="C261" s="41"/>
     </row>
     <row r="262" spans="1:3" ht="32" customHeight="1">
-      <c r="A262" s="39"/>
-      <c r="B262" s="38"/>
-      <c r="C262" s="63"/>
+      <c r="A262" s="47"/>
+      <c r="B262" s="44"/>
+      <c r="C262" s="41"/>
     </row>
     <row r="263" spans="1:3" ht="32" customHeight="1">
-      <c r="A263" s="39"/>
-      <c r="B263" s="38"/>
-      <c r="C263" s="63"/>
+      <c r="A263" s="47"/>
+      <c r="B263" s="44"/>
+      <c r="C263" s="41"/>
     </row>
     <row r="264" spans="1:3">
-      <c r="A264" s="39"/>
-      <c r="B264" s="38"/>
-      <c r="C264" s="63"/>
+      <c r="A264" s="47"/>
+      <c r="B264" s="44"/>
+      <c r="C264" s="41"/>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265" s="39"/>
-      <c r="B265" s="38"/>
-      <c r="C265" s="63"/>
+      <c r="A265" s="47"/>
+      <c r="B265" s="44"/>
+      <c r="C265" s="41"/>
     </row>
     <row r="266" spans="1:3">
-      <c r="A266" s="39"/>
-      <c r="B266" s="38"/>
-      <c r="C266" s="63"/>
+      <c r="A266" s="47"/>
+      <c r="B266" s="44"/>
+      <c r="C266" s="41"/>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="39"/>
-      <c r="B267" s="38"/>
-      <c r="C267" s="63"/>
+      <c r="A267" s="47"/>
+      <c r="B267" s="44"/>
+      <c r="C267" s="41"/>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="39"/>
-      <c r="B268" s="38"/>
-      <c r="C268" s="63"/>
+      <c r="A268" s="47"/>
+      <c r="B268" s="45"/>
+      <c r="C268" s="41"/>
     </row>
     <row r="269" spans="1:3">
-      <c r="A269" s="39"/>
-      <c r="B269" s="38"/>
-      <c r="C269" s="63"/>
+      <c r="A269" s="47"/>
+      <c r="B269" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C269" s="41"/>
     </row>
     <row r="270" spans="1:3">
-      <c r="A270" s="39"/>
-      <c r="B270" s="35"/>
-      <c r="C270" s="63"/>
+      <c r="A270" s="47"/>
+      <c r="B270" s="44"/>
+      <c r="C270" s="41"/>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="39"/>
-      <c r="B271" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C271" s="63"/>
+      <c r="A271" s="47"/>
+      <c r="B271" s="44"/>
+      <c r="C271" s="41"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="37"/>
-      <c r="B272" s="38"/>
-      <c r="C272" s="64"/>
+      <c r="A272" s="48"/>
+      <c r="B272" s="44"/>
+      <c r="C272" s="42"/>
     </row>
     <row r="273" spans="1:3" ht="306" customHeight="1">
-      <c r="A273" s="34" t="s">
+      <c r="A273" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="B273" s="38"/>
-      <c r="C273" s="62" t="s">
+      <c r="B273" s="44"/>
+      <c r="C273" s="40" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="274" spans="1:3">
-      <c r="A274" s="38"/>
-      <c r="B274" s="38"/>
-      <c r="C274" s="63"/>
+      <c r="A274" s="44"/>
+      <c r="B274" s="44"/>
+      <c r="C274" s="41"/>
     </row>
     <row r="275" spans="1:3" ht="48" customHeight="1">
-      <c r="A275" s="38"/>
-      <c r="B275" s="38"/>
-      <c r="C275" s="63"/>
+      <c r="A275" s="44"/>
+      <c r="B275" s="44"/>
+      <c r="C275" s="41"/>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="38"/>
-      <c r="B276" s="38"/>
-      <c r="C276" s="63"/>
+      <c r="A276" s="44"/>
+      <c r="B276" s="44"/>
+      <c r="C276" s="41"/>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="38"/>
-      <c r="B277" s="38"/>
-      <c r="C277" s="63"/>
+      <c r="A277" s="44"/>
+      <c r="B277" s="44"/>
+      <c r="C277" s="41"/>
     </row>
     <row r="278" spans="1:3">
-      <c r="A278" s="38"/>
-      <c r="B278" s="38"/>
-      <c r="C278" s="63"/>
+      <c r="A278" s="44"/>
+      <c r="B278" s="44"/>
+      <c r="C278" s="41"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="38"/>
-      <c r="B279" s="38"/>
-      <c r="C279" s="63"/>
+      <c r="A279" s="44"/>
+      <c r="B279" s="44"/>
+      <c r="C279" s="41"/>
     </row>
     <row r="280" spans="1:3" ht="32" customHeight="1">
-      <c r="A280" s="38"/>
-      <c r="B280" s="38"/>
-      <c r="C280" s="63"/>
+      <c r="A280" s="44"/>
+      <c r="B280" s="44"/>
+      <c r="C280" s="41"/>
     </row>
     <row r="281" spans="1:3">
-      <c r="A281" s="38"/>
-      <c r="B281" s="38"/>
-      <c r="C281" s="63"/>
+      <c r="A281" s="44"/>
+      <c r="B281" s="44"/>
+      <c r="C281" s="41"/>
     </row>
     <row r="282" spans="1:3">
-      <c r="A282" s="38"/>
-      <c r="B282" s="38"/>
-      <c r="C282" s="63"/>
+      <c r="A282" s="44"/>
+      <c r="B282" s="44"/>
+      <c r="C282" s="41"/>
     </row>
     <row r="283" spans="1:3">
-      <c r="A283" s="38"/>
-      <c r="B283" s="38"/>
-      <c r="C283" s="63"/>
+      <c r="A283" s="44"/>
+      <c r="B283" s="45"/>
+      <c r="C283" s="41"/>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="38"/>
-      <c r="B284" s="38"/>
-      <c r="C284" s="63"/>
+      <c r="A284" s="44"/>
+      <c r="C284" s="41"/>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="38"/>
-      <c r="B285" s="35"/>
-      <c r="C285" s="63"/>
+      <c r="A285" s="44"/>
+      <c r="C285" s="41"/>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286" s="38"/>
-      <c r="C286" s="63"/>
+      <c r="A286" s="44"/>
+      <c r="C286" s="41"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="38"/>
-      <c r="C287" s="64"/>
+      <c r="A287" s="44"/>
+      <c r="C287" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="C255:C256"/>
-    <mergeCell ref="C257:C272"/>
-    <mergeCell ref="C273:C287"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="C204:C211"/>
-    <mergeCell ref="C212:C223"/>
-    <mergeCell ref="C224:C227"/>
-    <mergeCell ref="C228:C244"/>
-    <mergeCell ref="C245:C254"/>
+  <mergeCells count="78">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A255:A256"/>
+    <mergeCell ref="B224:B240"/>
+    <mergeCell ref="A228:A244"/>
+    <mergeCell ref="B176:B197"/>
+    <mergeCell ref="A180:A201"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="B159:B168"/>
+    <mergeCell ref="A163:A172"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B241:B250"/>
+    <mergeCell ref="A245:A254"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="B169:B175"/>
+    <mergeCell ref="B125:B137"/>
+    <mergeCell ref="A129:A141"/>
+    <mergeCell ref="B138:B153"/>
+    <mergeCell ref="A142:A157"/>
+    <mergeCell ref="B99:B124"/>
+    <mergeCell ref="A103:A128"/>
+    <mergeCell ref="B9:B15"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B16:B30"/>
+    <mergeCell ref="B31:B41"/>
+    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="B42:B69"/>
+    <mergeCell ref="A46:A73"/>
+    <mergeCell ref="B70:B98"/>
+    <mergeCell ref="A74:A102"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B253:B268"/>
+    <mergeCell ref="A257:A272"/>
+    <mergeCell ref="B269:B283"/>
+    <mergeCell ref="A273:A287"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="B200:B207"/>
+    <mergeCell ref="A204:A211"/>
+    <mergeCell ref="B208:B219"/>
+    <mergeCell ref="A212:A223"/>
+    <mergeCell ref="B220:B223"/>
+    <mergeCell ref="A224:A227"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="A158:A160"/>
     <mergeCell ref="C180:C201"/>
     <mergeCell ref="C13:C19"/>
     <mergeCell ref="C35:C45"/>
@@ -7990,61 +8043,15 @@
     <mergeCell ref="C161:C162"/>
     <mergeCell ref="C163:C172"/>
     <mergeCell ref="C173:C179"/>
-    <mergeCell ref="B255:B270"/>
-    <mergeCell ref="A257:A272"/>
-    <mergeCell ref="B271:B285"/>
-    <mergeCell ref="A273:A287"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="B202:B209"/>
-    <mergeCell ref="A204:A211"/>
-    <mergeCell ref="B210:B221"/>
-    <mergeCell ref="A212:A223"/>
-    <mergeCell ref="B222:B225"/>
-    <mergeCell ref="A224:A227"/>
-    <mergeCell ref="B156:B158"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A35:A45"/>
-    <mergeCell ref="B44:B71"/>
-    <mergeCell ref="A46:A73"/>
-    <mergeCell ref="B72:B100"/>
-    <mergeCell ref="A74:A102"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B243:B252"/>
-    <mergeCell ref="A245:A254"/>
-    <mergeCell ref="B253:B254"/>
-    <mergeCell ref="B171:B177"/>
-    <mergeCell ref="B127:B139"/>
-    <mergeCell ref="A129:A141"/>
-    <mergeCell ref="B140:B155"/>
-    <mergeCell ref="A142:A157"/>
-    <mergeCell ref="B101:B126"/>
-    <mergeCell ref="A103:A128"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="B18:B32"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A255:A256"/>
-    <mergeCell ref="B226:B242"/>
-    <mergeCell ref="A228:A244"/>
-    <mergeCell ref="B178:B199"/>
-    <mergeCell ref="A180:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A173:A179"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="B161:B170"/>
-    <mergeCell ref="A163:A172"/>
+    <mergeCell ref="C255:C256"/>
+    <mergeCell ref="C257:C272"/>
+    <mergeCell ref="C273:C287"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="C204:C211"/>
+    <mergeCell ref="C212:C223"/>
+    <mergeCell ref="C224:C227"/>
+    <mergeCell ref="C228:C244"/>
+    <mergeCell ref="C245:C254"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8316,7 +8323,7 @@
       <c r="B24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="35" t="s">
         <v>52</v>
       </c>
     </row>
@@ -8599,7 +8606,7 @@
       <c r="A50" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="36" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="10" t="s">
@@ -8772,7 +8779,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" ht="85">
-      <c r="A66" s="69" t="s">
+      <c r="A66" s="37" t="s">
         <v>155</v>
       </c>
       <c r="B66" s="11" t="s">
